--- a/output_phyto/phyto_Intermediate_jasper_1994.xlsx
+++ b/output_phyto/phyto_Intermediate_jasper_1994.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="345">
   <si>
     <t>NA</t>
   </si>
@@ -1454,13 +1454,13 @@
     <t xml:space="preserve"/>
   </si>
   <si>
-    <t xml:space="preserve">phytoplankton_jasper_1994_1</t>
+    <t xml:space="preserve">phytoplankton_Jasper_1994_1</t>
   </si>
   <si>
     <t xml:space="preserve">10.1029/94PA02116</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.ncei.noaa.gov/pub/data/paleo/climate_forcing/trace_gases/Paleo-pCO2/phytoplankton_jasper_1994.xlsx</t>
+    <t xml:space="preserve">phytoplankton_jasper_1994_p1.0.xlsx</t>
   </si>
   <si>
     <t xml:space="preserve">Harper and Giulivi</t>
@@ -1475,205 +1475,208 @@
     <t xml:space="preserve">Mk37_2</t>
   </si>
   <si>
-    <t xml:space="preserve">alkenone unsaturation</t>
+    <t xml:space="preserve">published Uk37 temperature</t>
+  </si>
+  <si>
+    <t xml:space="preserve">estimate from WOA2018 at MANOP C</t>
   </si>
   <si>
     <t xml:space="preserve">Foraminfera vital effect is discussed but not reported. pCO2 error bars are included graphically, but data is not reported. The site is in the Equatorial Pacific upwelling region, so it is not used as an atmospheric CO2 record.</t>
   </si>
   <si>
-    <t xml:space="preserve">phytoplankton_jasper_1994_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_jasper_1994_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_jasper_1994_4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_jasper_1994_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_jasper_1994_6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_jasper_1994_7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_jasper_1994_8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_jasper_1994_9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_jasper_1994_10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_jasper_1994_11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_jasper_1994_12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_jasper_1994_13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_jasper_1994_14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_jasper_1994_15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_jasper_1994_16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_jasper_1994_17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_jasper_1994_18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_jasper_1994_19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_jasper_1994_20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_jasper_1994_21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_jasper_1994_22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_jasper_1994_23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_jasper_1994_24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_jasper_1994_25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_jasper_1994_26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_jasper_1994_27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_jasper_1994_28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_jasper_1994_29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_jasper_1994_30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_jasper_1994_31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_jasper_1994_32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_jasper_1994_33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_jasper_1994_34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_jasper_1994_35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_jasper_1994_36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_jasper_1994_37</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_jasper_1994_38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_jasper_1994_39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_jasper_1994_40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_jasper_1994_41</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_jasper_1994_42</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_jasper_1994_43</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_jasper_1994_44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_jasper_1994_45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_jasper_1994_46</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_jasper_1994_47</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_jasper_1994_48</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_jasper_1994_49</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_jasper_1994_50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_jasper_1994_51</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_jasper_1994_52</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_jasper_1994_53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_jasper_1994_54</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_jasper_1994_55</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_jasper_1994_56</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_jasper_1994_57</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_jasper_1994_58</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_jasper_1994_59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_jasper_1994_60</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_jasper_1994_61</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_jasper_1994_62</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_jasper_1994_63</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_jasper_1994_64</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_jasper_1994_65</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_jasper_1994_66</t>
+    <t xml:space="preserve">phytoplankton_Jasper_1994_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Jasper_1994_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Jasper_1994_4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Jasper_1994_5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Jasper_1994_6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Jasper_1994_7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Jasper_1994_8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Jasper_1994_9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Jasper_1994_10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Jasper_1994_11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Jasper_1994_12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Jasper_1994_13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Jasper_1994_14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Jasper_1994_15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Jasper_1994_16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Jasper_1994_17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Jasper_1994_18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Jasper_1994_19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Jasper_1994_20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Jasper_1994_21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Jasper_1994_22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Jasper_1994_23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Jasper_1994_24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Jasper_1994_25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Jasper_1994_26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Jasper_1994_27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Jasper_1994_28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Jasper_1994_29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Jasper_1994_30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Jasper_1994_31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Jasper_1994_32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Jasper_1994_33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Jasper_1994_34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Jasper_1994_35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Jasper_1994_36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Jasper_1994_37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Jasper_1994_38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Jasper_1994_39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Jasper_1994_40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Jasper_1994_41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Jasper_1994_42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Jasper_1994_43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Jasper_1994_44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Jasper_1994_45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Jasper_1994_46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Jasper_1994_47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Jasper_1994_48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Jasper_1994_49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Jasper_1994_50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Jasper_1994_51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Jasper_1994_52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Jasper_1994_53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Jasper_1994_54</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Jasper_1994_55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Jasper_1994_56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Jasper_1994_57</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Jasper_1994_58</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Jasper_1994_59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Jasper_1994_60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Jasper_1994_61</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Jasper_1994_62</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Jasper_1994_63</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Jasper_1994_64</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Jasper_1994_65</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phytoplankton_Jasper_1994_66</t>
   </si>
 </sst>
 </file>
@@ -1681,7 +1684,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="10">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1747,12 +1750,6 @@
       <name val="Arial"/>
       <family val="2"/>
       <b/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <u val="single"/>
     </font>
   </fonts>
   <fills count="10">
@@ -1866,7 +1863,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1965,7 +1962,6 @@
     <xf numFmtId="0" fontId="9" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2691,7 +2687,7 @@
       <c r="B5" t="s">
         <v>271</v>
       </c>
-      <c r="C5" s="34" t="s">
+      <c r="C5" t="s">
         <v>272</v>
       </c>
       <c r="D5" t="s">
@@ -2709,8 +2705,8 @@
       <c r="H5" t="n">
         <v>0.0008</v>
       </c>
-      <c r="I5" t="e">
-        <v>#N/A</v>
+      <c r="I5" t="n">
+        <v>0.004</v>
       </c>
       <c r="J5" t="e">
         <v>#N/A</v>
@@ -2728,7 +2724,7 @@
         <v>-26.1</v>
       </c>
       <c r="O5" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P5" t="e">
         <v>#N/A</v>
@@ -2739,8 +2735,8 @@
       <c r="R5" s="11" t="n">
         <v>27</v>
       </c>
-      <c r="S5" t="e">
-        <v>#N/A</v>
+      <c r="S5" t="n">
+        <v>3</v>
       </c>
       <c r="T5" t="e">
         <v>#N/A</v>
@@ -2751,35 +2747,35 @@
       <c r="V5" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="W5" t="e">
-        <v>#N/A</v>
+      <c r="W5" t="n">
+        <v>0.5</v>
       </c>
       <c r="X5" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AB5" t="e">
-        <v>#N/A</v>
+      <c r="Y5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC5" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF5" t="e">
-        <v>#N/A</v>
+      <c r="AD5" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG5" t="e">
         <v>#N/A</v>
@@ -2791,17 +2787,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="6" ht="19" customHeight="1">
       <c r="A6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B6" t="s">
         <v>271</v>
       </c>
-      <c r="C6" s="34" t="s">
+      <c r="C6" t="s">
         <v>272</v>
       </c>
       <c r="D6" t="s">
@@ -2819,8 +2815,8 @@
       <c r="H6" t="n">
         <v>0.0042</v>
       </c>
-      <c r="I6" t="e">
-        <v>#N/A</v>
+      <c r="I6" t="n">
+        <v>0.004</v>
       </c>
       <c r="J6" t="e">
         <v>#N/A</v>
@@ -2838,7 +2834,7 @@
         <v>-25.4</v>
       </c>
       <c r="O6" t="n">
-        <v>0.8</v>
+        <v>0.565685424949238</v>
       </c>
       <c r="P6" t="e">
         <v>#N/A</v>
@@ -2849,8 +2845,8 @@
       <c r="R6" s="11" t="n">
         <v>27.1</v>
       </c>
-      <c r="S6" t="e">
-        <v>#N/A</v>
+      <c r="S6" t="n">
+        <v>3</v>
       </c>
       <c r="T6" t="e">
         <v>#N/A</v>
@@ -2861,35 +2857,35 @@
       <c r="V6" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="W6" t="e">
-        <v>#N/A</v>
+      <c r="W6" t="n">
+        <v>0.5</v>
       </c>
       <c r="X6" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y6" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z6" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA6" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AB6" t="e">
-        <v>#N/A</v>
+      <c r="Y6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC6" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD6" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE6" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF6" t="e">
-        <v>#N/A</v>
+      <c r="AD6" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG6" t="e">
         <v>#N/A</v>
@@ -2901,17 +2897,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="7" ht="19" customHeight="1">
       <c r="A7" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B7" t="s">
         <v>271</v>
       </c>
-      <c r="C7" s="34" t="s">
+      <c r="C7" t="s">
         <v>272</v>
       </c>
       <c r="D7" t="s">
@@ -2929,8 +2925,8 @@
       <c r="H7" t="n">
         <v>0.0069</v>
       </c>
-      <c r="I7" t="e">
-        <v>#N/A</v>
+      <c r="I7" t="n">
+        <v>0.004</v>
       </c>
       <c r="J7" t="e">
         <v>#N/A</v>
@@ -2948,7 +2944,7 @@
         <v>-24.3</v>
       </c>
       <c r="O7" t="n">
-        <v>0.8</v>
+        <v>0.565685424949238</v>
       </c>
       <c r="P7" t="e">
         <v>#N/A</v>
@@ -2959,8 +2955,8 @@
       <c r="R7" s="11" t="n">
         <v>26.5</v>
       </c>
-      <c r="S7" t="e">
-        <v>#N/A</v>
+      <c r="S7" t="n">
+        <v>3</v>
       </c>
       <c r="T7" t="e">
         <v>#N/A</v>
@@ -2971,35 +2967,35 @@
       <c r="V7" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="W7" t="e">
-        <v>#N/A</v>
+      <c r="W7" t="n">
+        <v>0.5</v>
       </c>
       <c r="X7" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y7" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z7" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA7" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AB7" t="e">
-        <v>#N/A</v>
+      <c r="Y7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC7" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD7" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE7" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF7" t="e">
-        <v>#N/A</v>
+      <c r="AD7" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG7" t="e">
         <v>#N/A</v>
@@ -3011,17 +3007,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ7" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1">
       <c r="A8" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B8" t="s">
         <v>271</v>
       </c>
-      <c r="C8" s="34" t="s">
+      <c r="C8" t="s">
         <v>272</v>
       </c>
       <c r="D8" t="s">
@@ -3039,8 +3035,8 @@
       <c r="H8" t="n">
         <v>0.0107</v>
       </c>
-      <c r="I8" t="e">
-        <v>#N/A</v>
+      <c r="I8" t="n">
+        <v>0.004</v>
       </c>
       <c r="J8" t="e">
         <v>#N/A</v>
@@ -3058,7 +3054,7 @@
         <v>-24.3</v>
       </c>
       <c r="O8" t="n">
-        <v>0.8</v>
+        <v>0.565685424949238</v>
       </c>
       <c r="P8" t="e">
         <v>#N/A</v>
@@ -3069,8 +3065,8 @@
       <c r="R8" s="11" t="n">
         <v>26.6</v>
       </c>
-      <c r="S8" t="e">
-        <v>#N/A</v>
+      <c r="S8" t="n">
+        <v>3</v>
       </c>
       <c r="T8" t="e">
         <v>#N/A</v>
@@ -3081,35 +3077,35 @@
       <c r="V8" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="W8" t="e">
-        <v>#N/A</v>
+      <c r="W8" t="n">
+        <v>0.5</v>
       </c>
       <c r="X8" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AB8" t="e">
-        <v>#N/A</v>
+      <c r="Y8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC8" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF8" t="e">
-        <v>#N/A</v>
+      <c r="AD8" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG8" t="e">
         <v>#N/A</v>
@@ -3121,17 +3117,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ8" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="9" ht="19" customHeight="1">
       <c r="A9" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B9" t="s">
         <v>271</v>
       </c>
-      <c r="C9" s="34" t="s">
+      <c r="C9" t="s">
         <v>272</v>
       </c>
       <c r="D9" t="s">
@@ -3149,8 +3145,8 @@
       <c r="H9" t="n">
         <v>0.0121</v>
       </c>
-      <c r="I9" t="e">
-        <v>#N/A</v>
+      <c r="I9" t="n">
+        <v>0.004</v>
       </c>
       <c r="J9" t="e">
         <v>#N/A</v>
@@ -3168,7 +3164,7 @@
         <v>-24.6</v>
       </c>
       <c r="O9" t="n">
-        <v>0.8</v>
+        <v>0.565685424949238</v>
       </c>
       <c r="P9" t="e">
         <v>#N/A</v>
@@ -3179,8 +3175,8 @@
       <c r="R9" s="11" t="n">
         <v>26.7</v>
       </c>
-      <c r="S9" t="e">
-        <v>#N/A</v>
+      <c r="S9" t="n">
+        <v>3</v>
       </c>
       <c r="T9" t="e">
         <v>#N/A</v>
@@ -3191,35 +3187,35 @@
       <c r="V9" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="W9" t="e">
-        <v>#N/A</v>
+      <c r="W9" t="n">
+        <v>0.5</v>
       </c>
       <c r="X9" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y9" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z9" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA9" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AB9" t="e">
-        <v>#N/A</v>
+      <c r="Y9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC9" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD9" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE9" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF9" t="e">
-        <v>#N/A</v>
+      <c r="AD9" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG9" t="e">
         <v>#N/A</v>
@@ -3231,17 +3227,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ9" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1">
       <c r="A10" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B10" t="s">
         <v>271</v>
       </c>
-      <c r="C10" s="34" t="s">
+      <c r="C10" t="s">
         <v>272</v>
       </c>
       <c r="D10" t="s">
@@ -3259,8 +3255,8 @@
       <c r="H10" t="n">
         <v>0.0135</v>
       </c>
-      <c r="I10" t="e">
-        <v>#N/A</v>
+      <c r="I10" t="n">
+        <v>0.004</v>
       </c>
       <c r="J10" t="e">
         <v>#N/A</v>
@@ -3278,7 +3274,7 @@
         <v>-24.5</v>
       </c>
       <c r="O10" t="n">
-        <v>0.8</v>
+        <v>0.565685424949238</v>
       </c>
       <c r="P10" t="e">
         <v>#N/A</v>
@@ -3289,8 +3285,8 @@
       <c r="R10" s="11" t="n">
         <v>26.7</v>
       </c>
-      <c r="S10" t="e">
-        <v>#N/A</v>
+      <c r="S10" t="n">
+        <v>3</v>
       </c>
       <c r="T10" t="e">
         <v>#N/A</v>
@@ -3301,35 +3297,35 @@
       <c r="V10" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="W10" t="e">
-        <v>#N/A</v>
+      <c r="W10" t="n">
+        <v>0.5</v>
       </c>
       <c r="X10" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AB10" t="e">
-        <v>#N/A</v>
+      <c r="Y10" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC10" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF10" t="e">
-        <v>#N/A</v>
+      <c r="AD10" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG10" t="e">
         <v>#N/A</v>
@@ -3341,17 +3337,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ10" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1">
       <c r="A11" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B11" t="s">
         <v>271</v>
       </c>
-      <c r="C11" s="34" t="s">
+      <c r="C11" t="s">
         <v>272</v>
       </c>
       <c r="D11" t="s">
@@ -3369,8 +3365,8 @@
       <c r="H11" t="n">
         <v>0.0163</v>
       </c>
-      <c r="I11" t="e">
-        <v>#N/A</v>
+      <c r="I11" t="n">
+        <v>0.004</v>
       </c>
       <c r="J11" t="e">
         <v>#N/A</v>
@@ -3388,7 +3384,7 @@
         <v>-25.3</v>
       </c>
       <c r="O11" t="n">
-        <v>0.8</v>
+        <v>0.565685424949238</v>
       </c>
       <c r="P11" t="e">
         <v>#N/A</v>
@@ -3399,8 +3395,8 @@
       <c r="R11" s="11" t="n">
         <v>26.4</v>
       </c>
-      <c r="S11" t="e">
-        <v>#N/A</v>
+      <c r="S11" t="n">
+        <v>3</v>
       </c>
       <c r="T11" t="e">
         <v>#N/A</v>
@@ -3411,35 +3407,35 @@
       <c r="V11" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="W11" t="e">
-        <v>#N/A</v>
+      <c r="W11" t="n">
+        <v>0.5</v>
       </c>
       <c r="X11" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y11" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z11" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA11" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AB11" t="e">
-        <v>#N/A</v>
+      <c r="Y11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC11" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD11" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE11" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF11" t="e">
-        <v>#N/A</v>
+      <c r="AD11" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG11" t="e">
         <v>#N/A</v>
@@ -3451,17 +3447,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ11" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1">
       <c r="A12" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B12" t="s">
         <v>271</v>
       </c>
-      <c r="C12" s="34" t="s">
+      <c r="C12" t="s">
         <v>272</v>
       </c>
       <c r="D12" t="s">
@@ -3479,8 +3475,8 @@
       <c r="H12" t="n">
         <v>0.0177</v>
       </c>
-      <c r="I12" t="e">
-        <v>#N/A</v>
+      <c r="I12" t="n">
+        <v>0.004</v>
       </c>
       <c r="J12" t="e">
         <v>#N/A</v>
@@ -3498,7 +3494,7 @@
         <v>-24.6</v>
       </c>
       <c r="O12" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P12" t="e">
         <v>#N/A</v>
@@ -3509,8 +3505,8 @@
       <c r="R12" s="11" t="n">
         <v>26</v>
       </c>
-      <c r="S12" t="e">
-        <v>#N/A</v>
+      <c r="S12" t="n">
+        <v>3</v>
       </c>
       <c r="T12" t="e">
         <v>#N/A</v>
@@ -3521,35 +3517,35 @@
       <c r="V12" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="W12" t="e">
-        <v>#N/A</v>
+      <c r="W12" t="n">
+        <v>0.5</v>
       </c>
       <c r="X12" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y12" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z12" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA12" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AB12" t="e">
-        <v>#N/A</v>
+      <c r="Y12" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC12" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD12" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE12" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF12" t="e">
-        <v>#N/A</v>
+      <c r="AD12" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG12" t="e">
         <v>#N/A</v>
@@ -3561,17 +3557,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ12" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1">
       <c r="A13" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B13" t="s">
         <v>271</v>
       </c>
-      <c r="C13" s="34" t="s">
+      <c r="C13" t="s">
         <v>272</v>
       </c>
       <c r="D13" t="s">
@@ -3589,8 +3585,8 @@
       <c r="H13" t="n">
         <v>0.0191</v>
       </c>
-      <c r="I13" t="e">
-        <v>#N/A</v>
+      <c r="I13" t="n">
+        <v>0.004</v>
       </c>
       <c r="J13" t="e">
         <v>#N/A</v>
@@ -3608,7 +3604,7 @@
         <v>-24.6</v>
       </c>
       <c r="O13" t="n">
-        <v>0.8</v>
+        <v>0.565685424949238</v>
       </c>
       <c r="P13" t="e">
         <v>#N/A</v>
@@ -3619,8 +3615,8 @@
       <c r="R13" s="11" t="n">
         <v>25.8</v>
       </c>
-      <c r="S13" t="e">
-        <v>#N/A</v>
+      <c r="S13" t="n">
+        <v>3</v>
       </c>
       <c r="T13" t="e">
         <v>#N/A</v>
@@ -3631,35 +3627,35 @@
       <c r="V13" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="W13" t="e">
-        <v>#N/A</v>
+      <c r="W13" t="n">
+        <v>0.5</v>
       </c>
       <c r="X13" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AB13" t="e">
-        <v>#N/A</v>
+      <c r="Y13" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AA13" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC13" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF13" t="e">
-        <v>#N/A</v>
+      <c r="AD13" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG13" t="e">
         <v>#N/A</v>
@@ -3671,17 +3667,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ13" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1">
       <c r="A14" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B14" t="s">
         <v>271</v>
       </c>
-      <c r="C14" s="34" t="s">
+      <c r="C14" t="s">
         <v>272</v>
       </c>
       <c r="D14" t="s">
@@ -3699,8 +3695,8 @@
       <c r="H14" t="n">
         <v>0.0224</v>
       </c>
-      <c r="I14" t="e">
-        <v>#N/A</v>
+      <c r="I14" t="n">
+        <v>0.004</v>
       </c>
       <c r="J14" t="e">
         <v>#N/A</v>
@@ -3718,7 +3714,7 @@
         <v>-25.6</v>
       </c>
       <c r="O14" t="n">
-        <v>0.8</v>
+        <v>0.565685424949238</v>
       </c>
       <c r="P14" t="e">
         <v>#N/A</v>
@@ -3729,8 +3725,8 @@
       <c r="R14" s="11" t="n">
         <v>25.6</v>
       </c>
-      <c r="S14" t="e">
-        <v>#N/A</v>
+      <c r="S14" t="n">
+        <v>3</v>
       </c>
       <c r="T14" t="e">
         <v>#N/A</v>
@@ -3741,35 +3737,35 @@
       <c r="V14" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="W14" t="e">
-        <v>#N/A</v>
+      <c r="W14" t="n">
+        <v>0.5</v>
       </c>
       <c r="X14" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y14" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z14" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA14" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AB14" t="e">
-        <v>#N/A</v>
+      <c r="Y14" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AA14" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC14" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD14" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE14" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF14" t="e">
-        <v>#N/A</v>
+      <c r="AD14" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG14" t="e">
         <v>#N/A</v>
@@ -3781,17 +3777,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ14" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1">
       <c r="A15" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B15" t="s">
         <v>271</v>
       </c>
-      <c r="C15" s="34" t="s">
+      <c r="C15" t="s">
         <v>272</v>
       </c>
       <c r="D15" t="s">
@@ -3809,8 +3805,8 @@
       <c r="H15" t="n">
         <v>0.0255</v>
       </c>
-      <c r="I15" t="e">
-        <v>#N/A</v>
+      <c r="I15" t="n">
+        <v>0.004</v>
       </c>
       <c r="J15" t="e">
         <v>#N/A</v>
@@ -3828,7 +3824,7 @@
         <v>-25.4</v>
       </c>
       <c r="O15" t="n">
-        <v>0.8</v>
+        <v>0.565685424949238</v>
       </c>
       <c r="P15" t="e">
         <v>#N/A</v>
@@ -3839,8 +3835,8 @@
       <c r="R15" s="11" t="n">
         <v>25.3</v>
       </c>
-      <c r="S15" t="e">
-        <v>#N/A</v>
+      <c r="S15" t="n">
+        <v>3</v>
       </c>
       <c r="T15" t="e">
         <v>#N/A</v>
@@ -3851,35 +3847,35 @@
       <c r="V15" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="W15" t="e">
-        <v>#N/A</v>
+      <c r="W15" t="n">
+        <v>0.5</v>
       </c>
       <c r="X15" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y15" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z15" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA15" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AB15" t="e">
-        <v>#N/A</v>
+      <c r="Y15" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AA15" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC15" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD15" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE15" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF15" t="e">
-        <v>#N/A</v>
+      <c r="AD15" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG15" t="e">
         <v>#N/A</v>
@@ -3891,17 +3887,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ15" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="16" ht="19" customHeight="1">
       <c r="A16" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B16" t="s">
         <v>271</v>
       </c>
-      <c r="C16" s="34" t="s">
+      <c r="C16" t="s">
         <v>272</v>
       </c>
       <c r="D16" t="s">
@@ -3919,8 +3915,8 @@
       <c r="H16" t="n">
         <v>0.0284</v>
       </c>
-      <c r="I16" t="e">
-        <v>#N/A</v>
+      <c r="I16" t="n">
+        <v>0.004</v>
       </c>
       <c r="J16" t="e">
         <v>#N/A</v>
@@ -3938,7 +3934,7 @@
         <v>-24.8</v>
       </c>
       <c r="O16" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P16" t="e">
         <v>#N/A</v>
@@ -3949,8 +3945,8 @@
       <c r="R16" s="11" t="n">
         <v>25.3</v>
       </c>
-      <c r="S16" t="e">
-        <v>#N/A</v>
+      <c r="S16" t="n">
+        <v>3</v>
       </c>
       <c r="T16" t="e">
         <v>#N/A</v>
@@ -3961,35 +3957,35 @@
       <c r="V16" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="W16" t="e">
-        <v>#N/A</v>
+      <c r="W16" t="n">
+        <v>0.5</v>
       </c>
       <c r="X16" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y16" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z16" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA16" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AB16" t="e">
-        <v>#N/A</v>
+      <c r="Y16" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AA16" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC16" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD16" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE16" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF16" t="e">
-        <v>#N/A</v>
+      <c r="AD16" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG16" t="e">
         <v>#N/A</v>
@@ -4001,17 +3997,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ16" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1">
       <c r="A17" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B17" t="s">
         <v>271</v>
       </c>
-      <c r="C17" s="34" t="s">
+      <c r="C17" t="s">
         <v>272</v>
       </c>
       <c r="D17" t="s">
@@ -4029,8 +4025,8 @@
       <c r="H17" t="n">
         <v>0.0313</v>
       </c>
-      <c r="I17" t="e">
-        <v>#N/A</v>
+      <c r="I17" t="n">
+        <v>0.004</v>
       </c>
       <c r="J17" t="e">
         <v>#N/A</v>
@@ -4048,7 +4044,7 @@
         <v>-24.5</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4</v>
+        <v>0.282842712474619</v>
       </c>
       <c r="P17" t="e">
         <v>#N/A</v>
@@ -4059,8 +4055,8 @@
       <c r="R17" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="S17" t="e">
-        <v>#N/A</v>
+      <c r="S17" t="n">
+        <v>3</v>
       </c>
       <c r="T17" t="e">
         <v>#N/A</v>
@@ -4071,35 +4067,35 @@
       <c r="V17" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="W17" t="e">
-        <v>#N/A</v>
+      <c r="W17" t="n">
+        <v>0.5</v>
       </c>
       <c r="X17" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y17" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z17" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA17" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AB17" t="e">
-        <v>#N/A</v>
+      <c r="Y17" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AA17" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC17" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD17" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE17" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF17" t="e">
-        <v>#N/A</v>
+      <c r="AD17" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG17" t="e">
         <v>#N/A</v>
@@ -4111,17 +4107,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ17" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1">
       <c r="A18" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B18" t="s">
         <v>271</v>
       </c>
-      <c r="C18" s="34" t="s">
+      <c r="C18" t="s">
         <v>272</v>
       </c>
       <c r="D18" t="s">
@@ -4139,8 +4135,8 @@
       <c r="H18" t="n">
         <v>0.0336</v>
       </c>
-      <c r="I18" t="e">
-        <v>#N/A</v>
+      <c r="I18" t="n">
+        <v>0.004</v>
       </c>
       <c r="J18" t="e">
         <v>#N/A</v>
@@ -4158,7 +4154,7 @@
         <v>-25.1</v>
       </c>
       <c r="O18" t="n">
-        <v>0.8</v>
+        <v>0.565685424949238</v>
       </c>
       <c r="P18" t="e">
         <v>#N/A</v>
@@ -4169,8 +4165,8 @@
       <c r="R18" s="11" t="n">
         <v>25.3</v>
       </c>
-      <c r="S18" t="e">
-        <v>#N/A</v>
+      <c r="S18" t="n">
+        <v>3</v>
       </c>
       <c r="T18" t="e">
         <v>#N/A</v>
@@ -4181,35 +4177,35 @@
       <c r="V18" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="W18" t="e">
-        <v>#N/A</v>
+      <c r="W18" t="n">
+        <v>0.5</v>
       </c>
       <c r="X18" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y18" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z18" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA18" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AB18" t="e">
-        <v>#N/A</v>
+      <c r="Y18" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AA18" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC18" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD18" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE18" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF18" t="e">
-        <v>#N/A</v>
+      <c r="AD18" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG18" t="e">
         <v>#N/A</v>
@@ -4221,17 +4217,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ18" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="19" ht="19" customHeight="1">
       <c r="A19" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B19" t="s">
         <v>271</v>
       </c>
-      <c r="C19" s="34" t="s">
+      <c r="C19" t="s">
         <v>272</v>
       </c>
       <c r="D19" t="s">
@@ -4249,8 +4245,8 @@
       <c r="H19" t="n">
         <v>0.0372</v>
       </c>
-      <c r="I19" t="e">
-        <v>#N/A</v>
+      <c r="I19" t="n">
+        <v>0.004</v>
       </c>
       <c r="J19" t="e">
         <v>#N/A</v>
@@ -4268,7 +4264,7 @@
         <v>-25.5</v>
       </c>
       <c r="O19" t="n">
-        <v>0.8</v>
+        <v>0.565685424949238</v>
       </c>
       <c r="P19" t="e">
         <v>#N/A</v>
@@ -4279,8 +4275,8 @@
       <c r="R19" s="11" t="n">
         <v>24.7</v>
       </c>
-      <c r="S19" t="e">
-        <v>#N/A</v>
+      <c r="S19" t="n">
+        <v>3</v>
       </c>
       <c r="T19" t="e">
         <v>#N/A</v>
@@ -4291,35 +4287,35 @@
       <c r="V19" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="W19" t="e">
-        <v>#N/A</v>
+      <c r="W19" t="n">
+        <v>0.5</v>
       </c>
       <c r="X19" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y19" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z19" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA19" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AB19" t="e">
-        <v>#N/A</v>
+      <c r="Y19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AA19" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC19" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD19" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE19" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF19" t="e">
-        <v>#N/A</v>
+      <c r="AD19" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG19" t="e">
         <v>#N/A</v>
@@ -4331,17 +4327,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ19" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1">
       <c r="A20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B20" t="s">
         <v>271</v>
       </c>
-      <c r="C20" s="34" t="s">
+      <c r="C20" t="s">
         <v>272</v>
       </c>
       <c r="D20" t="s">
@@ -4359,8 +4355,8 @@
       <c r="H20" t="n">
         <v>0.0489</v>
       </c>
-      <c r="I20" t="e">
-        <v>#N/A</v>
+      <c r="I20" t="n">
+        <v>0.004</v>
       </c>
       <c r="J20" t="e">
         <v>#N/A</v>
@@ -4378,7 +4374,7 @@
         <v>-24.3</v>
       </c>
       <c r="O20" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P20" t="e">
         <v>#N/A</v>
@@ -4389,8 +4385,8 @@
       <c r="R20" s="11" t="n">
         <v>25.7</v>
       </c>
-      <c r="S20" t="e">
-        <v>#N/A</v>
+      <c r="S20" t="n">
+        <v>3</v>
       </c>
       <c r="T20" t="e">
         <v>#N/A</v>
@@ -4401,35 +4397,35 @@
       <c r="V20" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="W20" t="e">
-        <v>#N/A</v>
+      <c r="W20" t="n">
+        <v>0.5</v>
       </c>
       <c r="X20" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y20" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z20" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA20" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AB20" t="e">
-        <v>#N/A</v>
+      <c r="Y20" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AA20" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC20" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD20" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE20" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF20" t="e">
-        <v>#N/A</v>
+      <c r="AD20" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG20" t="e">
         <v>#N/A</v>
@@ -4441,17 +4437,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ20" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1">
       <c r="A21" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B21" t="s">
         <v>271</v>
       </c>
-      <c r="C21" s="34" t="s">
+      <c r="C21" t="s">
         <v>272</v>
       </c>
       <c r="D21" t="s">
@@ -4469,8 +4465,8 @@
       <c r="H21" t="n">
         <v>0.0547</v>
       </c>
-      <c r="I21" t="e">
-        <v>#N/A</v>
+      <c r="I21" t="n">
+        <v>0.004</v>
       </c>
       <c r="J21" t="e">
         <v>#N/A</v>
@@ -4488,7 +4484,7 @@
         <v>-24.4</v>
       </c>
       <c r="O21" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P21" t="e">
         <v>#N/A</v>
@@ -4499,8 +4495,8 @@
       <c r="R21" s="11" t="n">
         <v>25.9</v>
       </c>
-      <c r="S21" t="e">
-        <v>#N/A</v>
+      <c r="S21" t="n">
+        <v>3</v>
       </c>
       <c r="T21" t="e">
         <v>#N/A</v>
@@ -4511,35 +4507,35 @@
       <c r="V21" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="W21" t="e">
-        <v>#N/A</v>
+      <c r="W21" t="n">
+        <v>0.5</v>
       </c>
       <c r="X21" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y21" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z21" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA21" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AB21" t="e">
-        <v>#N/A</v>
+      <c r="Y21" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AA21" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC21" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD21" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE21" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF21" t="e">
-        <v>#N/A</v>
+      <c r="AD21" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG21" t="e">
         <v>#N/A</v>
@@ -4551,17 +4547,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ21" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="22" ht="19" customHeight="1">
       <c r="A22" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B22" t="s">
         <v>271</v>
       </c>
-      <c r="C22" s="34" t="s">
+      <c r="C22" t="s">
         <v>272</v>
       </c>
       <c r="D22" t="s">
@@ -4579,8 +4575,8 @@
       <c r="H22" t="n">
         <v>0.0553</v>
       </c>
-      <c r="I22" t="e">
-        <v>#N/A</v>
+      <c r="I22" t="n">
+        <v>0.004</v>
       </c>
       <c r="J22" t="e">
         <v>#N/A</v>
@@ -4598,7 +4594,7 @@
         <v>-24.6</v>
       </c>
       <c r="O22" t="n">
-        <v>0.8</v>
+        <v>0.565685424949238</v>
       </c>
       <c r="P22" t="e">
         <v>#N/A</v>
@@ -4609,8 +4605,8 @@
       <c r="R22" s="11" t="n">
         <v>25.8</v>
       </c>
-      <c r="S22" t="e">
-        <v>#N/A</v>
+      <c r="S22" t="n">
+        <v>3</v>
       </c>
       <c r="T22" t="e">
         <v>#N/A</v>
@@ -4621,35 +4617,35 @@
       <c r="V22" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="W22" t="e">
-        <v>#N/A</v>
+      <c r="W22" t="n">
+        <v>0.5</v>
       </c>
       <c r="X22" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y22" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z22" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA22" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AB22" t="e">
-        <v>#N/A</v>
+      <c r="Y22" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AA22" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC22" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD22" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE22" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF22" t="e">
-        <v>#N/A</v>
+      <c r="AD22" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG22" t="e">
         <v>#N/A</v>
@@ -4661,17 +4657,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ22" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="23" ht="19" customHeight="1">
       <c r="A23" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B23" t="s">
         <v>271</v>
       </c>
-      <c r="C23" s="34" t="s">
+      <c r="C23" t="s">
         <v>272</v>
       </c>
       <c r="D23" t="s">
@@ -4689,8 +4685,8 @@
       <c r="H23" t="n">
         <v>0.0576</v>
       </c>
-      <c r="I23" t="e">
-        <v>#N/A</v>
+      <c r="I23" t="n">
+        <v>0.004</v>
       </c>
       <c r="J23" t="e">
         <v>#N/A</v>
@@ -4708,7 +4704,7 @@
         <v>-25.6</v>
       </c>
       <c r="O23" t="n">
-        <v>0.8</v>
+        <v>0.565685424949238</v>
       </c>
       <c r="P23" t="e">
         <v>#N/A</v>
@@ -4719,8 +4715,8 @@
       <c r="R23" s="11" t="n">
         <v>25.6</v>
       </c>
-      <c r="S23" t="e">
-        <v>#N/A</v>
+      <c r="S23" t="n">
+        <v>3</v>
       </c>
       <c r="T23" t="e">
         <v>#N/A</v>
@@ -4731,35 +4727,35 @@
       <c r="V23" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="W23" t="e">
-        <v>#N/A</v>
+      <c r="W23" t="n">
+        <v>0.5</v>
       </c>
       <c r="X23" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AB23" t="e">
-        <v>#N/A</v>
+      <c r="Y23" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AA23" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC23" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF23" t="e">
-        <v>#N/A</v>
+      <c r="AD23" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG23" t="e">
         <v>#N/A</v>
@@ -4771,17 +4767,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ23" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="24" ht="19" customHeight="1">
       <c r="A24" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B24" t="s">
         <v>271</v>
       </c>
-      <c r="C24" s="34" t="s">
+      <c r="C24" t="s">
         <v>272</v>
       </c>
       <c r="D24" t="s">
@@ -4799,8 +4795,8 @@
       <c r="H24" t="n">
         <v>0.0611</v>
       </c>
-      <c r="I24" t="e">
-        <v>#N/A</v>
+      <c r="I24" t="n">
+        <v>0.004</v>
       </c>
       <c r="J24" t="e">
         <v>#N/A</v>
@@ -4818,7 +4814,7 @@
         <v>-25.4</v>
       </c>
       <c r="O24" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P24" t="e">
         <v>#N/A</v>
@@ -4829,8 +4825,8 @@
       <c r="R24" s="11" t="n">
         <v>26</v>
       </c>
-      <c r="S24" t="e">
-        <v>#N/A</v>
+      <c r="S24" t="n">
+        <v>3</v>
       </c>
       <c r="T24" t="e">
         <v>#N/A</v>
@@ -4841,35 +4837,35 @@
       <c r="V24" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="W24" t="e">
-        <v>#N/A</v>
+      <c r="W24" t="n">
+        <v>0.5</v>
       </c>
       <c r="X24" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AB24" t="e">
-        <v>#N/A</v>
+      <c r="Y24" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AA24" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC24" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF24" t="e">
-        <v>#N/A</v>
+      <c r="AD24" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG24" t="e">
         <v>#N/A</v>
@@ -4881,17 +4877,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ24" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="25" ht="19" customHeight="1">
       <c r="A25" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B25" t="s">
         <v>271</v>
       </c>
-      <c r="C25" s="34" t="s">
+      <c r="C25" t="s">
         <v>272</v>
       </c>
       <c r="D25" t="s">
@@ -4909,8 +4905,8 @@
       <c r="H25" t="n">
         <v>0.0635</v>
       </c>
-      <c r="I25" t="e">
-        <v>#N/A</v>
+      <c r="I25" t="n">
+        <v>0.004</v>
       </c>
       <c r="J25" t="e">
         <v>#N/A</v>
@@ -4928,7 +4924,7 @@
         <v>-25.1</v>
       </c>
       <c r="O25" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P25" t="e">
         <v>#N/A</v>
@@ -4939,8 +4935,8 @@
       <c r="R25" s="11" t="n">
         <v>26.2</v>
       </c>
-      <c r="S25" t="e">
-        <v>#N/A</v>
+      <c r="S25" t="n">
+        <v>3</v>
       </c>
       <c r="T25" t="e">
         <v>#N/A</v>
@@ -4951,35 +4947,35 @@
       <c r="V25" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="W25" t="e">
-        <v>#N/A</v>
+      <c r="W25" t="n">
+        <v>0.5</v>
       </c>
       <c r="X25" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y25" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z25" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA25" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AB25" t="e">
-        <v>#N/A</v>
+      <c r="Y25" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AA25" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC25" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD25" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE25" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF25" t="e">
-        <v>#N/A</v>
+      <c r="AD25" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG25" t="e">
         <v>#N/A</v>
@@ -4991,17 +4987,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ25" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="26" ht="19" customHeight="1">
       <c r="A26" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B26" t="s">
         <v>271</v>
       </c>
-      <c r="C26" s="34" t="s">
+      <c r="C26" t="s">
         <v>272</v>
       </c>
       <c r="D26" t="s">
@@ -5019,8 +5015,8 @@
       <c r="H26" t="n">
         <v>0.0641</v>
       </c>
-      <c r="I26" t="e">
-        <v>#N/A</v>
+      <c r="I26" t="n">
+        <v>0.004</v>
       </c>
       <c r="J26" t="e">
         <v>#N/A</v>
@@ -5038,7 +5034,7 @@
         <v>-24.4</v>
       </c>
       <c r="O26" t="n">
-        <v>0.8</v>
+        <v>0.565685424949238</v>
       </c>
       <c r="P26" t="e">
         <v>#N/A</v>
@@ -5049,8 +5045,8 @@
       <c r="R26" s="11" t="n">
         <v>26.1</v>
       </c>
-      <c r="S26" t="e">
-        <v>#N/A</v>
+      <c r="S26" t="n">
+        <v>3</v>
       </c>
       <c r="T26" t="e">
         <v>#N/A</v>
@@ -5061,35 +5057,35 @@
       <c r="V26" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="W26" t="e">
-        <v>#N/A</v>
+      <c r="W26" t="n">
+        <v>0.5</v>
       </c>
       <c r="X26" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AB26" t="e">
-        <v>#N/A</v>
+      <c r="Y26" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AA26" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC26" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF26" t="e">
-        <v>#N/A</v>
+      <c r="AD26" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG26" t="e">
         <v>#N/A</v>
@@ -5101,17 +5097,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ26" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="27" ht="19" customHeight="1">
       <c r="A27" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B27" t="s">
         <v>271</v>
       </c>
-      <c r="C27" s="34" t="s">
+      <c r="C27" t="s">
         <v>272</v>
       </c>
       <c r="D27" t="s">
@@ -5129,8 +5125,8 @@
       <c r="H27" t="n">
         <v>0.0665</v>
       </c>
-      <c r="I27" t="e">
-        <v>#N/A</v>
+      <c r="I27" t="n">
+        <v>0.004</v>
       </c>
       <c r="J27" t="e">
         <v>#N/A</v>
@@ -5148,7 +5144,7 @@
         <v>-24.9</v>
       </c>
       <c r="O27" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P27" t="e">
         <v>#N/A</v>
@@ -5159,8 +5155,8 @@
       <c r="R27" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="S27" t="e">
-        <v>#N/A</v>
+      <c r="S27" t="n">
+        <v>3</v>
       </c>
       <c r="T27" t="e">
         <v>#N/A</v>
@@ -5171,35 +5167,35 @@
       <c r="V27" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="W27" t="e">
-        <v>#N/A</v>
+      <c r="W27" t="n">
+        <v>0.5</v>
       </c>
       <c r="X27" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y27" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z27" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA27" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AB27" t="e">
-        <v>#N/A</v>
+      <c r="Y27" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AA27" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC27" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD27" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE27" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF27" t="e">
-        <v>#N/A</v>
+      <c r="AD27" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG27" t="e">
         <v>#N/A</v>
@@ -5211,17 +5207,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ27" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="28" ht="19" customHeight="1">
       <c r="A28" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B28" t="s">
         <v>271</v>
       </c>
-      <c r="C28" s="34" t="s">
+      <c r="C28" t="s">
         <v>272</v>
       </c>
       <c r="D28" t="s">
@@ -5239,8 +5235,8 @@
       <c r="H28" t="n">
         <v>0.0684</v>
       </c>
-      <c r="I28" t="e">
-        <v>#N/A</v>
+      <c r="I28" t="n">
+        <v>0.004</v>
       </c>
       <c r="J28" t="e">
         <v>#N/A</v>
@@ -5258,7 +5254,7 @@
         <v>-24.3</v>
       </c>
       <c r="O28" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P28" t="e">
         <v>#N/A</v>
@@ -5269,8 +5265,8 @@
       <c r="R28" s="11" t="n">
         <v>25.7</v>
       </c>
-      <c r="S28" t="e">
-        <v>#N/A</v>
+      <c r="S28" t="n">
+        <v>3</v>
       </c>
       <c r="T28" t="e">
         <v>#N/A</v>
@@ -5281,35 +5277,35 @@
       <c r="V28" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="W28" t="e">
-        <v>#N/A</v>
+      <c r="W28" t="n">
+        <v>0.5</v>
       </c>
       <c r="X28" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y28" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z28" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA28" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AB28" t="e">
-        <v>#N/A</v>
+      <c r="Y28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AA28" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC28" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD28" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE28" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF28" t="e">
-        <v>#N/A</v>
+      <c r="AD28" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG28" t="e">
         <v>#N/A</v>
@@ -5321,17 +5317,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ28" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="29" ht="19" customHeight="1">
       <c r="A29" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B29" t="s">
         <v>271</v>
       </c>
-      <c r="C29" s="34" t="s">
+      <c r="C29" t="s">
         <v>272</v>
       </c>
       <c r="D29" t="s">
@@ -5349,8 +5345,8 @@
       <c r="H29" t="n">
         <v>0.0703</v>
       </c>
-      <c r="I29" t="e">
-        <v>#N/A</v>
+      <c r="I29" t="n">
+        <v>0.004</v>
       </c>
       <c r="J29" t="e">
         <v>#N/A</v>
@@ -5368,7 +5364,7 @@
         <v>-23.9</v>
       </c>
       <c r="O29" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P29" t="e">
         <v>#N/A</v>
@@ -5379,8 +5375,8 @@
       <c r="R29" s="11" t="n">
         <v>25.9</v>
       </c>
-      <c r="S29" t="e">
-        <v>#N/A</v>
+      <c r="S29" t="n">
+        <v>3</v>
       </c>
       <c r="T29" t="e">
         <v>#N/A</v>
@@ -5391,35 +5387,35 @@
       <c r="V29" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="W29" t="e">
-        <v>#N/A</v>
+      <c r="W29" t="n">
+        <v>0.5</v>
       </c>
       <c r="X29" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y29" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z29" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA29" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AB29" t="e">
-        <v>#N/A</v>
+      <c r="Y29" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AA29" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC29" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD29" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE29" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF29" t="e">
-        <v>#N/A</v>
+      <c r="AD29" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG29" t="e">
         <v>#N/A</v>
@@ -5431,17 +5427,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ29" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="30" ht="19" customHeight="1">
       <c r="A30" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B30" t="s">
         <v>271</v>
       </c>
-      <c r="C30" s="34" t="s">
+      <c r="C30" t="s">
         <v>272</v>
       </c>
       <c r="D30" t="s">
@@ -5459,8 +5455,8 @@
       <c r="H30" t="n">
         <v>0.0729</v>
       </c>
-      <c r="I30" t="e">
-        <v>#N/A</v>
+      <c r="I30" t="n">
+        <v>0.004</v>
       </c>
       <c r="J30" t="e">
         <v>#N/A</v>
@@ -5478,7 +5474,7 @@
         <v>-25.7</v>
       </c>
       <c r="O30" t="n">
-        <v>0.8</v>
+        <v>0.565685424949238</v>
       </c>
       <c r="P30" t="e">
         <v>#N/A</v>
@@ -5489,8 +5485,8 @@
       <c r="R30" s="11" t="n">
         <v>25.2</v>
       </c>
-      <c r="S30" t="e">
-        <v>#N/A</v>
+      <c r="S30" t="n">
+        <v>3</v>
       </c>
       <c r="T30" t="e">
         <v>#N/A</v>
@@ -5501,35 +5497,35 @@
       <c r="V30" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="W30" t="e">
-        <v>#N/A</v>
+      <c r="W30" t="n">
+        <v>0.5</v>
       </c>
       <c r="X30" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y30" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z30" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA30" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AB30" t="e">
-        <v>#N/A</v>
+      <c r="Y30" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AA30" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC30" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD30" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE30" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF30" t="e">
-        <v>#N/A</v>
+      <c r="AD30" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG30" t="e">
         <v>#N/A</v>
@@ -5541,17 +5537,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ30" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="31" ht="19" customHeight="1">
       <c r="A31" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B31" t="s">
         <v>271</v>
       </c>
-      <c r="C31" s="34" t="s">
+      <c r="C31" t="s">
         <v>272</v>
       </c>
       <c r="D31" t="s">
@@ -5569,8 +5565,8 @@
       <c r="H31" t="n">
         <v>0.0746</v>
       </c>
-      <c r="I31" t="e">
-        <v>#N/A</v>
+      <c r="I31" t="n">
+        <v>0.004</v>
       </c>
       <c r="J31" t="e">
         <v>#N/A</v>
@@ -5588,7 +5584,7 @@
         <v>-25.3</v>
       </c>
       <c r="O31" t="n">
-        <v>0.8</v>
+        <v>0.565685424949238</v>
       </c>
       <c r="P31" t="e">
         <v>#N/A</v>
@@ -5599,8 +5595,8 @@
       <c r="R31" s="11" t="n">
         <v>25.6</v>
       </c>
-      <c r="S31" t="e">
-        <v>#N/A</v>
+      <c r="S31" t="n">
+        <v>3</v>
       </c>
       <c r="T31" t="e">
         <v>#N/A</v>
@@ -5611,35 +5607,35 @@
       <c r="V31" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="W31" t="e">
-        <v>#N/A</v>
+      <c r="W31" t="n">
+        <v>0.5</v>
       </c>
       <c r="X31" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y31" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z31" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA31" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AB31" t="e">
-        <v>#N/A</v>
+      <c r="Y31" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AA31" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC31" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD31" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE31" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF31" t="e">
-        <v>#N/A</v>
+      <c r="AD31" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG31" t="e">
         <v>#N/A</v>
@@ -5651,17 +5647,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ31" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="32" ht="19" customHeight="1">
       <c r="A32" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B32" t="s">
         <v>271</v>
       </c>
-      <c r="C32" s="34" t="s">
+      <c r="C32" t="s">
         <v>272</v>
       </c>
       <c r="D32" t="s">
@@ -5679,8 +5675,8 @@
       <c r="H32" t="n">
         <v>0.0758</v>
       </c>
-      <c r="I32" t="e">
-        <v>#N/A</v>
+      <c r="I32" t="n">
+        <v>0.004</v>
       </c>
       <c r="J32" t="e">
         <v>#N/A</v>
@@ -5698,7 +5694,7 @@
         <v>-24.9</v>
       </c>
       <c r="O32" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P32" t="e">
         <v>#N/A</v>
@@ -5709,8 +5705,8 @@
       <c r="R32" s="11" t="n">
         <v>26</v>
       </c>
-      <c r="S32" t="e">
-        <v>#N/A</v>
+      <c r="S32" t="n">
+        <v>3</v>
       </c>
       <c r="T32" t="e">
         <v>#N/A</v>
@@ -5721,35 +5717,35 @@
       <c r="V32" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="W32" t="e">
-        <v>#N/A</v>
+      <c r="W32" t="n">
+        <v>0.5</v>
       </c>
       <c r="X32" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y32" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z32" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA32" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AB32" t="e">
-        <v>#N/A</v>
+      <c r="Y32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AA32" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC32" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD32" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE32" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF32" t="e">
-        <v>#N/A</v>
+      <c r="AD32" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG32" t="e">
         <v>#N/A</v>
@@ -5761,17 +5757,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ32" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="33" ht="19" customHeight="1">
       <c r="A33" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B33" t="s">
         <v>271</v>
       </c>
-      <c r="C33" s="34" t="s">
+      <c r="C33" t="s">
         <v>272</v>
       </c>
       <c r="D33" t="s">
@@ -5789,8 +5785,8 @@
       <c r="H33" t="n">
         <v>0.0789</v>
       </c>
-      <c r="I33" t="e">
-        <v>#N/A</v>
+      <c r="I33" t="n">
+        <v>0.004</v>
       </c>
       <c r="J33" t="e">
         <v>#N/A</v>
@@ -5808,7 +5804,7 @@
         <v>-25.2</v>
       </c>
       <c r="O33" t="n">
-        <v>0.8</v>
+        <v>0.565685424949238</v>
       </c>
       <c r="P33" t="e">
         <v>#N/A</v>
@@ -5819,8 +5815,8 @@
       <c r="R33" s="11" t="n">
         <v>25.6</v>
       </c>
-      <c r="S33" t="e">
-        <v>#N/A</v>
+      <c r="S33" t="n">
+        <v>3</v>
       </c>
       <c r="T33" t="e">
         <v>#N/A</v>
@@ -5831,35 +5827,35 @@
       <c r="V33" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="W33" t="e">
-        <v>#N/A</v>
+      <c r="W33" t="n">
+        <v>0.5</v>
       </c>
       <c r="X33" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AB33" t="e">
-        <v>#N/A</v>
+      <c r="Y33" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AA33" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC33" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF33" t="e">
-        <v>#N/A</v>
+      <c r="AD33" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG33" t="e">
         <v>#N/A</v>
@@ -5871,17 +5867,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ33" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="34" ht="19" customHeight="1">
       <c r="A34" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B34" t="s">
         <v>271</v>
       </c>
-      <c r="C34" s="34" t="s">
+      <c r="C34" t="s">
         <v>272</v>
       </c>
       <c r="D34" t="s">
@@ -5899,8 +5895,8 @@
       <c r="H34" t="n">
         <v>0.0812</v>
       </c>
-      <c r="I34" t="e">
-        <v>#N/A</v>
+      <c r="I34" t="n">
+        <v>0.004</v>
       </c>
       <c r="J34" t="e">
         <v>#N/A</v>
@@ -5918,7 +5914,7 @@
         <v>-26.6</v>
       </c>
       <c r="O34" t="n">
-        <v>0.8</v>
+        <v>0.565685424949238</v>
       </c>
       <c r="P34" t="e">
         <v>#N/A</v>
@@ -5929,8 +5925,8 @@
       <c r="R34" s="11" t="n">
         <v>25.7</v>
       </c>
-      <c r="S34" t="e">
-        <v>#N/A</v>
+      <c r="S34" t="n">
+        <v>3</v>
       </c>
       <c r="T34" t="e">
         <v>#N/A</v>
@@ -5941,35 +5937,35 @@
       <c r="V34" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="W34" t="e">
-        <v>#N/A</v>
+      <c r="W34" t="n">
+        <v>0.5</v>
       </c>
       <c r="X34" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y34" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z34" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA34" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AB34" t="e">
-        <v>#N/A</v>
+      <c r="Y34" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AA34" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC34" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD34" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE34" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF34" t="e">
-        <v>#N/A</v>
+      <c r="AD34" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG34" t="e">
         <v>#N/A</v>
@@ -5981,17 +5977,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ34" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="35" ht="19" customHeight="1">
       <c r="A35" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B35" t="s">
         <v>271</v>
       </c>
-      <c r="C35" s="34" t="s">
+      <c r="C35" t="s">
         <v>272</v>
       </c>
       <c r="D35" t="s">
@@ -6009,8 +6005,8 @@
       <c r="H35" t="n">
         <v>0.0858</v>
       </c>
-      <c r="I35" t="e">
-        <v>#N/A</v>
+      <c r="I35" t="n">
+        <v>0.004</v>
       </c>
       <c r="J35" t="e">
         <v>#N/A</v>
@@ -6028,7 +6024,7 @@
         <v>-26.4</v>
       </c>
       <c r="O35" t="n">
-        <v>0.8</v>
+        <v>0.565685424949238</v>
       </c>
       <c r="P35" t="e">
         <v>#N/A</v>
@@ -6039,8 +6035,8 @@
       <c r="R35" s="11" t="n">
         <v>26.2</v>
       </c>
-      <c r="S35" t="e">
-        <v>#N/A</v>
+      <c r="S35" t="n">
+        <v>3</v>
       </c>
       <c r="T35" t="e">
         <v>#N/A</v>
@@ -6051,35 +6047,35 @@
       <c r="V35" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="W35" t="e">
-        <v>#N/A</v>
+      <c r="W35" t="n">
+        <v>0.5</v>
       </c>
       <c r="X35" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y35" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z35" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA35" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AB35" t="e">
-        <v>#N/A</v>
+      <c r="Y35" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AA35" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC35" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD35" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE35" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF35" t="e">
-        <v>#N/A</v>
+      <c r="AD35" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG35" t="e">
         <v>#N/A</v>
@@ -6091,17 +6087,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ35" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="36" ht="19" customHeight="1">
       <c r="A36" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B36" t="s">
         <v>271</v>
       </c>
-      <c r="C36" s="34" t="s">
+      <c r="C36" t="s">
         <v>272</v>
       </c>
       <c r="D36" t="s">
@@ -6119,8 +6115,8 @@
       <c r="H36" t="n">
         <v>0.0919</v>
       </c>
-      <c r="I36" t="e">
-        <v>#N/A</v>
+      <c r="I36" t="n">
+        <v>0.004</v>
       </c>
       <c r="J36" t="e">
         <v>#N/A</v>
@@ -6138,7 +6134,7 @@
         <v>-25.7</v>
       </c>
       <c r="O36" t="n">
-        <v>0.8</v>
+        <v>0.565685424949238</v>
       </c>
       <c r="P36" t="e">
         <v>#N/A</v>
@@ -6149,8 +6145,8 @@
       <c r="R36" s="11" t="n">
         <v>25.9</v>
       </c>
-      <c r="S36" t="e">
-        <v>#N/A</v>
+      <c r="S36" t="n">
+        <v>3</v>
       </c>
       <c r="T36" t="e">
         <v>#N/A</v>
@@ -6161,35 +6157,35 @@
       <c r="V36" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="W36" t="e">
-        <v>#N/A</v>
+      <c r="W36" t="n">
+        <v>0.5</v>
       </c>
       <c r="X36" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y36" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z36" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA36" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AB36" t="e">
-        <v>#N/A</v>
+      <c r="Y36" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AA36" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC36" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD36" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE36" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF36" t="e">
-        <v>#N/A</v>
+      <c r="AD36" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG36" t="e">
         <v>#N/A</v>
@@ -6201,17 +6197,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ36" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="37" ht="19" customHeight="1">
       <c r="A37" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B37" t="s">
         <v>271</v>
       </c>
-      <c r="C37" s="34" t="s">
+      <c r="C37" t="s">
         <v>272</v>
       </c>
       <c r="D37" t="s">
@@ -6229,8 +6225,8 @@
       <c r="H37" t="n">
         <v>0.1081</v>
       </c>
-      <c r="I37" t="e">
-        <v>#N/A</v>
+      <c r="I37" t="n">
+        <v>0.004</v>
       </c>
       <c r="J37" t="e">
         <v>#N/A</v>
@@ -6248,7 +6244,7 @@
         <v>-25.1</v>
       </c>
       <c r="O37" t="n">
-        <v>0.8</v>
+        <v>0.565685424949238</v>
       </c>
       <c r="P37" t="e">
         <v>#N/A</v>
@@ -6259,8 +6255,8 @@
       <c r="R37" s="11" t="n">
         <v>26.5</v>
       </c>
-      <c r="S37" t="e">
-        <v>#N/A</v>
+      <c r="S37" t="n">
+        <v>3</v>
       </c>
       <c r="T37" t="e">
         <v>#N/A</v>
@@ -6271,35 +6267,35 @@
       <c r="V37" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="W37" t="e">
-        <v>#N/A</v>
+      <c r="W37" t="n">
+        <v>0.5</v>
       </c>
       <c r="X37" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y37" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z37" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA37" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AB37" t="e">
-        <v>#N/A</v>
+      <c r="Y37" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AA37" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC37" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD37" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE37" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF37" t="e">
-        <v>#N/A</v>
+      <c r="AD37" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG37" t="e">
         <v>#N/A</v>
@@ -6311,17 +6307,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ37" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="38" ht="19" customHeight="1">
       <c r="A38" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B38" t="s">
         <v>271</v>
       </c>
-      <c r="C38" s="34" t="s">
+      <c r="C38" t="s">
         <v>272</v>
       </c>
       <c r="D38" t="s">
@@ -6339,8 +6335,8 @@
       <c r="H38" t="n">
         <v>0.1229</v>
       </c>
-      <c r="I38" t="e">
-        <v>#N/A</v>
+      <c r="I38" t="n">
+        <v>0.004</v>
       </c>
       <c r="J38" t="e">
         <v>#N/A</v>
@@ -6358,7 +6354,7 @@
         <v>-25.1</v>
       </c>
       <c r="O38" t="n">
-        <v>0.8</v>
+        <v>0.565685424949238</v>
       </c>
       <c r="P38" t="e">
         <v>#N/A</v>
@@ -6369,8 +6365,8 @@
       <c r="R38" s="11" t="n">
         <v>27.2</v>
       </c>
-      <c r="S38" t="e">
-        <v>#N/A</v>
+      <c r="S38" t="n">
+        <v>3</v>
       </c>
       <c r="T38" t="e">
         <v>#N/A</v>
@@ -6381,35 +6377,35 @@
       <c r="V38" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="W38" t="e">
-        <v>#N/A</v>
+      <c r="W38" t="n">
+        <v>0.5</v>
       </c>
       <c r="X38" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y38" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z38" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA38" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AB38" t="e">
-        <v>#N/A</v>
+      <c r="Y38" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AA38" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC38" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD38" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE38" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF38" t="e">
-        <v>#N/A</v>
+      <c r="AD38" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG38" t="e">
         <v>#N/A</v>
@@ -6421,17 +6417,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ38" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="39" ht="19" customHeight="1">
       <c r="A39" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B39" t="s">
         <v>271</v>
       </c>
-      <c r="C39" s="34" t="s">
+      <c r="C39" t="s">
         <v>272</v>
       </c>
       <c r="D39" t="s">
@@ -6449,8 +6445,8 @@
       <c r="H39" t="n">
         <v>0.1297</v>
       </c>
-      <c r="I39" t="e">
-        <v>#N/A</v>
+      <c r="I39" t="n">
+        <v>0.004</v>
       </c>
       <c r="J39" t="e">
         <v>#N/A</v>
@@ -6468,7 +6464,7 @@
         <v>-25.9</v>
       </c>
       <c r="O39" t="n">
-        <v>0.8</v>
+        <v>0.565685424949238</v>
       </c>
       <c r="P39" t="e">
         <v>#N/A</v>
@@ -6479,8 +6475,8 @@
       <c r="R39" s="11" t="n">
         <v>26.8</v>
       </c>
-      <c r="S39" t="e">
-        <v>#N/A</v>
+      <c r="S39" t="n">
+        <v>3</v>
       </c>
       <c r="T39" t="e">
         <v>#N/A</v>
@@ -6491,35 +6487,35 @@
       <c r="V39" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="W39" t="e">
-        <v>#N/A</v>
+      <c r="W39" t="n">
+        <v>0.5</v>
       </c>
       <c r="X39" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y39" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z39" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA39" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AB39" t="e">
-        <v>#N/A</v>
+      <c r="Y39" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AA39" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC39" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD39" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE39" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF39" t="e">
-        <v>#N/A</v>
+      <c r="AD39" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG39" t="e">
         <v>#N/A</v>
@@ -6531,17 +6527,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ39" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="40" ht="19" customHeight="1">
       <c r="A40" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B40" t="s">
         <v>271</v>
       </c>
-      <c r="C40" s="34" t="s">
+      <c r="C40" t="s">
         <v>272</v>
       </c>
       <c r="D40" t="s">
@@ -6559,8 +6555,8 @@
       <c r="H40" t="n">
         <v>0.1398</v>
       </c>
-      <c r="I40" t="e">
-        <v>#N/A</v>
+      <c r="I40" t="n">
+        <v>0.004</v>
       </c>
       <c r="J40" t="e">
         <v>#N/A</v>
@@ -6578,7 +6574,7 @@
         <v>-25.2</v>
       </c>
       <c r="O40" t="n">
-        <v>0.8</v>
+        <v>0.565685424949238</v>
       </c>
       <c r="P40" t="e">
         <v>#N/A</v>
@@ -6589,8 +6585,8 @@
       <c r="R40" s="11" t="n">
         <v>26.5</v>
       </c>
-      <c r="S40" t="e">
-        <v>#N/A</v>
+      <c r="S40" t="n">
+        <v>3</v>
       </c>
       <c r="T40" t="e">
         <v>#N/A</v>
@@ -6601,35 +6597,35 @@
       <c r="V40" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="W40" t="e">
-        <v>#N/A</v>
+      <c r="W40" t="n">
+        <v>0.5</v>
       </c>
       <c r="X40" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y40" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z40" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA40" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AB40" t="e">
-        <v>#N/A</v>
+      <c r="Y40" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AA40" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC40" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD40" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE40" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF40" t="e">
-        <v>#N/A</v>
+      <c r="AD40" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG40" t="e">
         <v>#N/A</v>
@@ -6641,17 +6637,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ40" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="41" ht="19" customHeight="1">
       <c r="A41" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B41" t="s">
         <v>271</v>
       </c>
-      <c r="C41" s="34" t="s">
+      <c r="C41" t="s">
         <v>272</v>
       </c>
       <c r="D41" t="s">
@@ -6669,8 +6665,8 @@
       <c r="H41" t="n">
         <v>0.1437</v>
       </c>
-      <c r="I41" t="e">
-        <v>#N/A</v>
+      <c r="I41" t="n">
+        <v>0.004</v>
       </c>
       <c r="J41" t="e">
         <v>#N/A</v>
@@ -6688,7 +6684,7 @@
         <v>-24.8</v>
       </c>
       <c r="O41" t="n">
-        <v>0.8</v>
+        <v>0.565685424949238</v>
       </c>
       <c r="P41" t="e">
         <v>#N/A</v>
@@ -6699,8 +6695,8 @@
       <c r="R41" s="11" t="n">
         <v>25.3</v>
       </c>
-      <c r="S41" t="e">
-        <v>#N/A</v>
+      <c r="S41" t="n">
+        <v>3</v>
       </c>
       <c r="T41" t="e">
         <v>#N/A</v>
@@ -6711,35 +6707,35 @@
       <c r="V41" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="W41" t="e">
-        <v>#N/A</v>
+      <c r="W41" t="n">
+        <v>0.5</v>
       </c>
       <c r="X41" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y41" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z41" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA41" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AB41" t="e">
-        <v>#N/A</v>
+      <c r="Y41" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AA41" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC41" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD41" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE41" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF41" t="e">
-        <v>#N/A</v>
+      <c r="AD41" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG41" t="e">
         <v>#N/A</v>
@@ -6751,17 +6747,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ41" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="42" ht="19" customHeight="1">
       <c r="A42" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B42" t="s">
         <v>271</v>
       </c>
-      <c r="C42" s="34" t="s">
+      <c r="C42" t="s">
         <v>272</v>
       </c>
       <c r="D42" t="s">
@@ -6779,8 +6775,8 @@
       <c r="H42" t="n">
         <v>0.1443</v>
       </c>
-      <c r="I42" t="e">
-        <v>#N/A</v>
+      <c r="I42" t="n">
+        <v>0.004</v>
       </c>
       <c r="J42" t="e">
         <v>#N/A</v>
@@ -6798,7 +6794,7 @@
         <v>-25.1</v>
       </c>
       <c r="O42" t="n">
-        <v>0.8</v>
+        <v>0.565685424949238</v>
       </c>
       <c r="P42" t="e">
         <v>#N/A</v>
@@ -6809,8 +6805,8 @@
       <c r="R42" s="11" t="n">
         <v>26</v>
       </c>
-      <c r="S42" t="e">
-        <v>#N/A</v>
+      <c r="S42" t="n">
+        <v>3</v>
       </c>
       <c r="T42" t="e">
         <v>#N/A</v>
@@ -6821,35 +6817,35 @@
       <c r="V42" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="W42" t="e">
-        <v>#N/A</v>
+      <c r="W42" t="n">
+        <v>0.5</v>
       </c>
       <c r="X42" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y42" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z42" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA42" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AB42" t="e">
-        <v>#N/A</v>
+      <c r="Y42" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AA42" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC42" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD42" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE42" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF42" t="e">
-        <v>#N/A</v>
+      <c r="AD42" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG42" t="e">
         <v>#N/A</v>
@@ -6861,17 +6857,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ42" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="43" ht="19" customHeight="1">
       <c r="A43" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B43" t="s">
         <v>271</v>
       </c>
-      <c r="C43" s="34" t="s">
+      <c r="C43" t="s">
         <v>272</v>
       </c>
       <c r="D43" t="s">
@@ -6889,8 +6885,8 @@
       <c r="H43" t="n">
         <v>0.1462</v>
       </c>
-      <c r="I43" t="e">
-        <v>#N/A</v>
+      <c r="I43" t="n">
+        <v>0.004</v>
       </c>
       <c r="J43" t="e">
         <v>#N/A</v>
@@ -6908,7 +6904,7 @@
         <v>-23.5</v>
       </c>
       <c r="O43" t="n">
-        <v>0.8</v>
+        <v>0.565685424949238</v>
       </c>
       <c r="P43" t="e">
         <v>#N/A</v>
@@ -6919,8 +6915,8 @@
       <c r="R43" s="11" t="n">
         <v>25.6</v>
       </c>
-      <c r="S43" t="e">
-        <v>#N/A</v>
+      <c r="S43" t="n">
+        <v>3</v>
       </c>
       <c r="T43" t="e">
         <v>#N/A</v>
@@ -6931,35 +6927,35 @@
       <c r="V43" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="W43" t="e">
-        <v>#N/A</v>
+      <c r="W43" t="n">
+        <v>0.5</v>
       </c>
       <c r="X43" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y43" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z43" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA43" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AB43" t="e">
-        <v>#N/A</v>
+      <c r="Y43" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AA43" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC43" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD43" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE43" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF43" t="e">
-        <v>#N/A</v>
+      <c r="AD43" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG43" t="e">
         <v>#N/A</v>
@@ -6971,17 +6967,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ43" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="44" ht="19" customHeight="1">
       <c r="A44" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B44" t="s">
         <v>271</v>
       </c>
-      <c r="C44" s="34" t="s">
+      <c r="C44" t="s">
         <v>272</v>
       </c>
       <c r="D44" t="s">
@@ -6999,8 +6995,8 @@
       <c r="H44" t="n">
         <v>0.1501</v>
       </c>
-      <c r="I44" t="e">
-        <v>#N/A</v>
+      <c r="I44" t="n">
+        <v>0.004</v>
       </c>
       <c r="J44" t="e">
         <v>#N/A</v>
@@ -7018,7 +7014,7 @@
         <v>-24.1</v>
       </c>
       <c r="O44" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P44" t="e">
         <v>#N/A</v>
@@ -7029,8 +7025,8 @@
       <c r="R44" s="11" t="n">
         <v>25.9</v>
       </c>
-      <c r="S44" t="e">
-        <v>#N/A</v>
+      <c r="S44" t="n">
+        <v>3</v>
       </c>
       <c r="T44" t="e">
         <v>#N/A</v>
@@ -7041,35 +7037,35 @@
       <c r="V44" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="W44" t="e">
-        <v>#N/A</v>
+      <c r="W44" t="n">
+        <v>0.5</v>
       </c>
       <c r="X44" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y44" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z44" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA44" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AB44" t="e">
-        <v>#N/A</v>
+      <c r="Y44" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AA44" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC44" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD44" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE44" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF44" t="e">
-        <v>#N/A</v>
+      <c r="AD44" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG44" t="e">
         <v>#N/A</v>
@@ -7081,17 +7077,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ44" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="45" ht="19" customHeight="1">
       <c r="A45" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B45" t="s">
         <v>271</v>
       </c>
-      <c r="C45" s="34" t="s">
+      <c r="C45" t="s">
         <v>272</v>
       </c>
       <c r="D45" t="s">
@@ -7109,8 +7105,8 @@
       <c r="H45" t="n">
         <v>0.1523</v>
       </c>
-      <c r="I45" t="e">
-        <v>#N/A</v>
+      <c r="I45" t="n">
+        <v>0.004</v>
       </c>
       <c r="J45" t="e">
         <v>#N/A</v>
@@ -7128,7 +7124,7 @@
         <v>-24.2</v>
       </c>
       <c r="O45" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P45" t="e">
         <v>#N/A</v>
@@ -7139,8 +7135,8 @@
       <c r="R45" s="11" t="n">
         <v>25.8</v>
       </c>
-      <c r="S45" t="e">
-        <v>#N/A</v>
+      <c r="S45" t="n">
+        <v>3</v>
       </c>
       <c r="T45" t="e">
         <v>#N/A</v>
@@ -7151,35 +7147,35 @@
       <c r="V45" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="W45" t="e">
-        <v>#N/A</v>
+      <c r="W45" t="n">
+        <v>0.5</v>
       </c>
       <c r="X45" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y45" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z45" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA45" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AB45" t="e">
-        <v>#N/A</v>
+      <c r="Y45" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AA45" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC45" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD45" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE45" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF45" t="e">
-        <v>#N/A</v>
+      <c r="AD45" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG45" t="e">
         <v>#N/A</v>
@@ -7191,17 +7187,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ45" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="46" ht="19" customHeight="1">
       <c r="A46" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B46" t="s">
         <v>271</v>
       </c>
-      <c r="C46" s="34" t="s">
+      <c r="C46" t="s">
         <v>272</v>
       </c>
       <c r="D46" t="s">
@@ -7219,8 +7215,8 @@
       <c r="H46" t="n">
         <v>0.1558</v>
       </c>
-      <c r="I46" t="e">
-        <v>#N/A</v>
+      <c r="I46" t="n">
+        <v>0.004</v>
       </c>
       <c r="J46" t="e">
         <v>#N/A</v>
@@ -7238,7 +7234,7 @@
         <v>-24.4</v>
       </c>
       <c r="O46" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P46" t="e">
         <v>#N/A</v>
@@ -7249,8 +7245,8 @@
       <c r="R46" s="11" t="n">
         <v>25.6</v>
       </c>
-      <c r="S46" t="e">
-        <v>#N/A</v>
+      <c r="S46" t="n">
+        <v>3</v>
       </c>
       <c r="T46" t="e">
         <v>#N/A</v>
@@ -7261,35 +7257,35 @@
       <c r="V46" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="W46" t="e">
-        <v>#N/A</v>
+      <c r="W46" t="n">
+        <v>0.5</v>
       </c>
       <c r="X46" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y46" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z46" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA46" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AB46" t="e">
-        <v>#N/A</v>
+      <c r="Y46" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AA46" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC46" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD46" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE46" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF46" t="e">
-        <v>#N/A</v>
+      <c r="AD46" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG46" t="e">
         <v>#N/A</v>
@@ -7301,17 +7297,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ46" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="47" ht="19" customHeight="1">
       <c r="A47" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B47" t="s">
         <v>271</v>
       </c>
-      <c r="C47" s="34" t="s">
+      <c r="C47" t="s">
         <v>272</v>
       </c>
       <c r="D47" t="s">
@@ -7329,8 +7325,8 @@
       <c r="H47" t="n">
         <v>0.1601</v>
       </c>
-      <c r="I47" t="e">
-        <v>#N/A</v>
+      <c r="I47" t="n">
+        <v>0.004</v>
       </c>
       <c r="J47" t="e">
         <v>#N/A</v>
@@ -7348,7 +7344,7 @@
         <v>-24.3</v>
       </c>
       <c r="O47" t="n">
-        <v>0.4</v>
+        <v>0.282842712474619</v>
       </c>
       <c r="P47" t="e">
         <v>#N/A</v>
@@ -7359,8 +7355,8 @@
       <c r="R47" s="11" t="n">
         <v>25.8</v>
       </c>
-      <c r="S47" t="e">
-        <v>#N/A</v>
+      <c r="S47" t="n">
+        <v>3</v>
       </c>
       <c r="T47" t="e">
         <v>#N/A</v>
@@ -7371,35 +7367,35 @@
       <c r="V47" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="W47" t="e">
-        <v>#N/A</v>
+      <c r="W47" t="n">
+        <v>0.5</v>
       </c>
       <c r="X47" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y47" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z47" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA47" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AB47" t="e">
-        <v>#N/A</v>
+      <c r="Y47" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AA47" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC47" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD47" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE47" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF47" t="e">
-        <v>#N/A</v>
+      <c r="AD47" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG47" t="e">
         <v>#N/A</v>
@@ -7411,17 +7407,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ47" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="48" ht="19" customHeight="1">
       <c r="A48" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B48" t="s">
         <v>271</v>
       </c>
-      <c r="C48" s="34" t="s">
+      <c r="C48" t="s">
         <v>272</v>
       </c>
       <c r="D48" t="s">
@@ -7439,8 +7435,8 @@
       <c r="H48" t="n">
         <v>0.161</v>
       </c>
-      <c r="I48" t="e">
-        <v>#N/A</v>
+      <c r="I48" t="n">
+        <v>0.004</v>
       </c>
       <c r="J48" t="e">
         <v>#N/A</v>
@@ -7458,7 +7454,7 @@
         <v>-24.6</v>
       </c>
       <c r="O48" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P48" t="e">
         <v>#N/A</v>
@@ -7469,8 +7465,8 @@
       <c r="R48" s="11" t="n">
         <v>25.3</v>
       </c>
-      <c r="S48" t="e">
-        <v>#N/A</v>
+      <c r="S48" t="n">
+        <v>3</v>
       </c>
       <c r="T48" t="e">
         <v>#N/A</v>
@@ -7481,35 +7477,35 @@
       <c r="V48" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="W48" t="e">
-        <v>#N/A</v>
+      <c r="W48" t="n">
+        <v>0.5</v>
       </c>
       <c r="X48" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y48" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z48" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA48" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AB48" t="e">
-        <v>#N/A</v>
+      <c r="Y48" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AA48" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC48" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD48" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE48" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF48" t="e">
-        <v>#N/A</v>
+      <c r="AD48" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG48" t="e">
         <v>#N/A</v>
@@ -7521,17 +7517,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ48" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="49" ht="19" customHeight="1">
       <c r="A49" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B49" t="s">
         <v>271</v>
       </c>
-      <c r="C49" s="34" t="s">
+      <c r="C49" t="s">
         <v>272</v>
       </c>
       <c r="D49" t="s">
@@ -7549,8 +7545,8 @@
       <c r="H49" t="n">
         <v>0.1653</v>
       </c>
-      <c r="I49" t="e">
-        <v>#N/A</v>
+      <c r="I49" t="n">
+        <v>0.004</v>
       </c>
       <c r="J49" t="e">
         <v>#N/A</v>
@@ -7568,7 +7564,7 @@
         <v>-24.5</v>
       </c>
       <c r="O49" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P49" t="e">
         <v>#N/A</v>
@@ -7579,8 +7575,8 @@
       <c r="R49" s="11" t="n">
         <v>25.6</v>
       </c>
-      <c r="S49" t="e">
-        <v>#N/A</v>
+      <c r="S49" t="n">
+        <v>3</v>
       </c>
       <c r="T49" t="e">
         <v>#N/A</v>
@@ -7591,35 +7587,35 @@
       <c r="V49" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="W49" t="e">
-        <v>#N/A</v>
+      <c r="W49" t="n">
+        <v>0.5</v>
       </c>
       <c r="X49" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y49" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z49" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA49" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AB49" t="e">
-        <v>#N/A</v>
+      <c r="Y49" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AA49" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC49" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD49" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE49" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF49" t="e">
-        <v>#N/A</v>
+      <c r="AD49" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG49" t="e">
         <v>#N/A</v>
@@ -7631,17 +7627,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ49" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="50" ht="19" customHeight="1">
       <c r="A50" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B50" t="s">
         <v>271</v>
       </c>
-      <c r="C50" s="34" t="s">
+      <c r="C50" t="s">
         <v>272</v>
       </c>
       <c r="D50" t="s">
@@ -7659,8 +7655,8 @@
       <c r="H50" t="n">
         <v>0.1665</v>
       </c>
-      <c r="I50" t="e">
-        <v>#N/A</v>
+      <c r="I50" t="n">
+        <v>0.004</v>
       </c>
       <c r="J50" t="e">
         <v>#N/A</v>
@@ -7678,7 +7674,7 @@
         <v>-25.3</v>
       </c>
       <c r="O50" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P50" t="e">
         <v>#N/A</v>
@@ -7689,8 +7685,8 @@
       <c r="R50" s="11" t="n">
         <v>25.6</v>
       </c>
-      <c r="S50" t="e">
-        <v>#N/A</v>
+      <c r="S50" t="n">
+        <v>3</v>
       </c>
       <c r="T50" t="e">
         <v>#N/A</v>
@@ -7701,35 +7697,35 @@
       <c r="V50" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="W50" t="e">
-        <v>#N/A</v>
+      <c r="W50" t="n">
+        <v>0.5</v>
       </c>
       <c r="X50" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y50" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z50" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA50" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AB50" t="e">
-        <v>#N/A</v>
+      <c r="Y50" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AA50" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC50" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD50" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE50" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF50" t="e">
-        <v>#N/A</v>
+      <c r="AD50" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG50" t="e">
         <v>#N/A</v>
@@ -7741,17 +7737,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ50" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="51" ht="19" customHeight="1">
       <c r="A51" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B51" t="s">
         <v>271</v>
       </c>
-      <c r="C51" s="34" t="s">
+      <c r="C51" t="s">
         <v>272</v>
       </c>
       <c r="D51" t="s">
@@ -7769,8 +7765,8 @@
       <c r="H51" t="n">
         <v>0.1701</v>
       </c>
-      <c r="I51" t="e">
-        <v>#N/A</v>
+      <c r="I51" t="n">
+        <v>0.004</v>
       </c>
       <c r="J51" t="e">
         <v>#N/A</v>
@@ -7788,7 +7784,7 @@
         <v>-24.9</v>
       </c>
       <c r="O51" t="n">
-        <v>0.8</v>
+        <v>0.565685424949238</v>
       </c>
       <c r="P51" t="e">
         <v>#N/A</v>
@@ -7799,8 +7795,8 @@
       <c r="R51" s="11" t="n">
         <v>25.3</v>
       </c>
-      <c r="S51" t="e">
-        <v>#N/A</v>
+      <c r="S51" t="n">
+        <v>3</v>
       </c>
       <c r="T51" t="e">
         <v>#N/A</v>
@@ -7811,35 +7807,35 @@
       <c r="V51" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="W51" t="e">
-        <v>#N/A</v>
+      <c r="W51" t="n">
+        <v>0.5</v>
       </c>
       <c r="X51" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y51" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z51" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA51" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AB51" t="e">
-        <v>#N/A</v>
+      <c r="Y51" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AA51" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC51" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD51" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE51" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF51" t="e">
-        <v>#N/A</v>
+      <c r="AD51" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG51" t="e">
         <v>#N/A</v>
@@ -7851,17 +7847,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ51" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="52" ht="19" customHeight="1">
       <c r="A52" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B52" t="s">
         <v>271</v>
       </c>
-      <c r="C52" s="34" t="s">
+      <c r="C52" t="s">
         <v>272</v>
       </c>
       <c r="D52" t="s">
@@ -7879,8 +7875,8 @@
       <c r="H52" t="n">
         <v>0.1737</v>
       </c>
-      <c r="I52" t="e">
-        <v>#N/A</v>
+      <c r="I52" t="n">
+        <v>0.004</v>
       </c>
       <c r="J52" t="e">
         <v>#N/A</v>
@@ -7898,7 +7894,7 @@
         <v>-24.5</v>
       </c>
       <c r="O52" t="n">
-        <v>0.4</v>
+        <v>0.282842712474619</v>
       </c>
       <c r="P52" t="e">
         <v>#N/A</v>
@@ -7909,8 +7905,8 @@
       <c r="R52" s="11" t="n">
         <v>26.2</v>
       </c>
-      <c r="S52" t="e">
-        <v>#N/A</v>
+      <c r="S52" t="n">
+        <v>3</v>
       </c>
       <c r="T52" t="e">
         <v>#N/A</v>
@@ -7921,35 +7917,35 @@
       <c r="V52" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="W52" t="e">
-        <v>#N/A</v>
+      <c r="W52" t="n">
+        <v>0.5</v>
       </c>
       <c r="X52" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y52" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z52" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA52" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AB52" t="e">
-        <v>#N/A</v>
+      <c r="Y52" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AA52" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC52" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD52" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE52" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF52" t="e">
-        <v>#N/A</v>
+      <c r="AD52" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG52" t="e">
         <v>#N/A</v>
@@ -7961,17 +7957,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ52" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="53" ht="19" customHeight="1">
       <c r="A53" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B53" t="s">
         <v>271</v>
       </c>
-      <c r="C53" s="34" t="s">
+      <c r="C53" t="s">
         <v>272</v>
       </c>
       <c r="D53" t="s">
@@ -7989,8 +7985,8 @@
       <c r="H53" t="n">
         <v>0.176</v>
       </c>
-      <c r="I53" t="e">
-        <v>#N/A</v>
+      <c r="I53" t="n">
+        <v>0.004</v>
       </c>
       <c r="J53" t="e">
         <v>#N/A</v>
@@ -8008,7 +8004,7 @@
         <v>-25.9</v>
       </c>
       <c r="O53" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P53" t="e">
         <v>#N/A</v>
@@ -8019,8 +8015,8 @@
       <c r="R53" s="11" t="n">
         <v>26.3</v>
       </c>
-      <c r="S53" t="e">
-        <v>#N/A</v>
+      <c r="S53" t="n">
+        <v>3</v>
       </c>
       <c r="T53" t="e">
         <v>#N/A</v>
@@ -8031,35 +8027,35 @@
       <c r="V53" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="W53" t="e">
-        <v>#N/A</v>
+      <c r="W53" t="n">
+        <v>0.5</v>
       </c>
       <c r="X53" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y53" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z53" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA53" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AB53" t="e">
-        <v>#N/A</v>
+      <c r="Y53" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AA53" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC53" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD53" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE53" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF53" t="e">
-        <v>#N/A</v>
+      <c r="AD53" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG53" t="e">
         <v>#N/A</v>
@@ -8071,17 +8067,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ53" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="54" ht="19" customHeight="1">
       <c r="A54" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B54" t="s">
         <v>271</v>
       </c>
-      <c r="C54" s="34" t="s">
+      <c r="C54" t="s">
         <v>272</v>
       </c>
       <c r="D54" t="s">
@@ -8099,8 +8095,8 @@
       <c r="H54" t="n">
         <v>0.1767</v>
       </c>
-      <c r="I54" t="e">
-        <v>#N/A</v>
+      <c r="I54" t="n">
+        <v>0.004</v>
       </c>
       <c r="J54" t="e">
         <v>#N/A</v>
@@ -8118,7 +8114,7 @@
         <v>-25.2</v>
       </c>
       <c r="O54" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P54" t="e">
         <v>#N/A</v>
@@ -8129,8 +8125,8 @@
       <c r="R54" s="11" t="n">
         <v>25.6</v>
       </c>
-      <c r="S54" t="e">
-        <v>#N/A</v>
+      <c r="S54" t="n">
+        <v>3</v>
       </c>
       <c r="T54" t="e">
         <v>#N/A</v>
@@ -8141,35 +8137,35 @@
       <c r="V54" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="W54" t="e">
-        <v>#N/A</v>
+      <c r="W54" t="n">
+        <v>0.5</v>
       </c>
       <c r="X54" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y54" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z54" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA54" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AB54" t="e">
-        <v>#N/A</v>
+      <c r="Y54" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AA54" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC54" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD54" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE54" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF54" t="e">
-        <v>#N/A</v>
+      <c r="AD54" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG54" t="e">
         <v>#N/A</v>
@@ -8181,17 +8177,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ54" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="55" ht="19" customHeight="1">
       <c r="A55" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B55" t="s">
         <v>271</v>
       </c>
-      <c r="C55" s="34" t="s">
+      <c r="C55" t="s">
         <v>272</v>
       </c>
       <c r="D55" t="s">
@@ -8209,8 +8205,8 @@
       <c r="H55" t="n">
         <v>0.1797</v>
       </c>
-      <c r="I55" t="e">
-        <v>#N/A</v>
+      <c r="I55" t="n">
+        <v>0.004</v>
       </c>
       <c r="J55" t="e">
         <v>#N/A</v>
@@ -8228,7 +8224,7 @@
         <v>-24.9</v>
       </c>
       <c r="O55" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P55" t="e">
         <v>#N/A</v>
@@ -8239,8 +8235,8 @@
       <c r="R55" s="11" t="n">
         <v>25.6</v>
       </c>
-      <c r="S55" t="e">
-        <v>#N/A</v>
+      <c r="S55" t="n">
+        <v>3</v>
       </c>
       <c r="T55" t="e">
         <v>#N/A</v>
@@ -8251,35 +8247,35 @@
       <c r="V55" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="W55" t="e">
-        <v>#N/A</v>
+      <c r="W55" t="n">
+        <v>0.5</v>
       </c>
       <c r="X55" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y55" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z55" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA55" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AB55" t="e">
-        <v>#N/A</v>
+      <c r="Y55" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AA55" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC55" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD55" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE55" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF55" t="e">
-        <v>#N/A</v>
+      <c r="AD55" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG55" t="e">
         <v>#N/A</v>
@@ -8291,17 +8287,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ55" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="56" ht="19" customHeight="1">
       <c r="A56" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B56" t="s">
         <v>271</v>
       </c>
-      <c r="C56" s="34" t="s">
+      <c r="C56" t="s">
         <v>272</v>
       </c>
       <c r="D56" t="s">
@@ -8319,8 +8315,8 @@
       <c r="H56" t="n">
         <v>0.182</v>
       </c>
-      <c r="I56" t="e">
-        <v>#N/A</v>
+      <c r="I56" t="n">
+        <v>0.004</v>
       </c>
       <c r="J56" t="e">
         <v>#N/A</v>
@@ -8338,7 +8334,7 @@
         <v>-24.2</v>
       </c>
       <c r="O56" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P56" t="e">
         <v>#N/A</v>
@@ -8349,8 +8345,8 @@
       <c r="R56" s="11" t="n">
         <v>25.8</v>
       </c>
-      <c r="S56" t="e">
-        <v>#N/A</v>
+      <c r="S56" t="n">
+        <v>3</v>
       </c>
       <c r="T56" t="e">
         <v>#N/A</v>
@@ -8361,35 +8357,35 @@
       <c r="V56" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="W56" t="e">
-        <v>#N/A</v>
+      <c r="W56" t="n">
+        <v>0.5</v>
       </c>
       <c r="X56" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y56" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z56" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA56" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AB56" t="e">
-        <v>#N/A</v>
+      <c r="Y56" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AA56" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC56" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD56" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE56" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF56" t="e">
-        <v>#N/A</v>
+      <c r="AD56" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG56" t="e">
         <v>#N/A</v>
@@ -8401,17 +8397,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ56" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="57" ht="19" customHeight="1">
       <c r="A57" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B57" t="s">
         <v>271</v>
       </c>
-      <c r="C57" s="34" t="s">
+      <c r="C57" t="s">
         <v>272</v>
       </c>
       <c r="D57" t="s">
@@ -8429,8 +8425,8 @@
       <c r="H57" t="n">
         <v>0.1839</v>
       </c>
-      <c r="I57" t="e">
-        <v>#N/A</v>
+      <c r="I57" t="n">
+        <v>0.004</v>
       </c>
       <c r="J57" t="e">
         <v>#N/A</v>
@@ -8448,7 +8444,7 @@
         <v>-24.3</v>
       </c>
       <c r="O57" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P57" t="e">
         <v>#N/A</v>
@@ -8459,8 +8455,8 @@
       <c r="R57" s="11" t="n">
         <v>25.9</v>
       </c>
-      <c r="S57" t="e">
-        <v>#N/A</v>
+      <c r="S57" t="n">
+        <v>3</v>
       </c>
       <c r="T57" t="e">
         <v>#N/A</v>
@@ -8471,35 +8467,35 @@
       <c r="V57" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="W57" t="e">
-        <v>#N/A</v>
+      <c r="W57" t="n">
+        <v>0.5</v>
       </c>
       <c r="X57" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y57" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z57" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA57" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AB57" t="e">
-        <v>#N/A</v>
+      <c r="Y57" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AA57" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC57" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD57" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE57" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF57" t="e">
-        <v>#N/A</v>
+      <c r="AD57" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG57" t="e">
         <v>#N/A</v>
@@ -8511,17 +8507,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ57" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="58" ht="19" customHeight="1">
       <c r="A58" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B58" t="s">
         <v>271</v>
       </c>
-      <c r="C58" s="34" t="s">
+      <c r="C58" t="s">
         <v>272</v>
       </c>
       <c r="D58" t="s">
@@ -8539,8 +8535,8 @@
       <c r="H58" t="n">
         <v>0.1945</v>
       </c>
-      <c r="I58" t="e">
-        <v>#N/A</v>
+      <c r="I58" t="n">
+        <v>0.004</v>
       </c>
       <c r="J58" t="e">
         <v>#N/A</v>
@@ -8558,7 +8554,7 @@
         <v>-25.4</v>
       </c>
       <c r="O58" t="n">
-        <v>0.8</v>
+        <v>0.565685424949238</v>
       </c>
       <c r="P58" t="e">
         <v>#N/A</v>
@@ -8569,8 +8565,8 @@
       <c r="R58" s="11" t="n">
         <v>25.9</v>
       </c>
-      <c r="S58" t="e">
-        <v>#N/A</v>
+      <c r="S58" t="n">
+        <v>3</v>
       </c>
       <c r="T58" t="e">
         <v>#N/A</v>
@@ -8581,35 +8577,35 @@
       <c r="V58" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="W58" t="e">
-        <v>#N/A</v>
+      <c r="W58" t="n">
+        <v>0.5</v>
       </c>
       <c r="X58" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y58" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z58" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA58" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AB58" t="e">
-        <v>#N/A</v>
+      <c r="Y58" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AA58" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC58" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD58" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE58" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF58" t="e">
-        <v>#N/A</v>
+      <c r="AD58" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE58" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF58" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG58" t="e">
         <v>#N/A</v>
@@ -8621,17 +8617,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ58" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="59" ht="19" customHeight="1">
       <c r="A59" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B59" t="s">
         <v>271</v>
       </c>
-      <c r="C59" s="34" t="s">
+      <c r="C59" t="s">
         <v>272</v>
       </c>
       <c r="D59" t="s">
@@ -8649,8 +8645,8 @@
       <c r="H59" t="n">
         <v>0.1985</v>
       </c>
-      <c r="I59" t="e">
-        <v>#N/A</v>
+      <c r="I59" t="n">
+        <v>0.004</v>
       </c>
       <c r="J59" t="e">
         <v>#N/A</v>
@@ -8668,7 +8664,7 @@
         <v>-25.6</v>
       </c>
       <c r="O59" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P59" t="e">
         <v>#N/A</v>
@@ -8679,8 +8675,8 @@
       <c r="R59" s="11" t="n">
         <v>26.2</v>
       </c>
-      <c r="S59" t="e">
-        <v>#N/A</v>
+      <c r="S59" t="n">
+        <v>3</v>
       </c>
       <c r="T59" t="e">
         <v>#N/A</v>
@@ -8691,35 +8687,35 @@
       <c r="V59" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="W59" t="e">
-        <v>#N/A</v>
+      <c r="W59" t="n">
+        <v>0.5</v>
       </c>
       <c r="X59" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y59" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z59" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA59" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AB59" t="e">
-        <v>#N/A</v>
+      <c r="Y59" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AA59" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC59" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD59" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE59" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF59" t="e">
-        <v>#N/A</v>
+      <c r="AD59" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE59" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF59" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG59" t="e">
         <v>#N/A</v>
@@ -8731,17 +8727,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ59" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="60" ht="19" customHeight="1">
       <c r="A60" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B60" t="s">
         <v>271</v>
       </c>
-      <c r="C60" s="34" t="s">
+      <c r="C60" t="s">
         <v>272</v>
       </c>
       <c r="D60" t="s">
@@ -8759,8 +8755,8 @@
       <c r="H60" t="n">
         <v>0.2</v>
       </c>
-      <c r="I60" t="e">
-        <v>#N/A</v>
+      <c r="I60" t="n">
+        <v>0.004</v>
       </c>
       <c r="J60" t="e">
         <v>#N/A</v>
@@ -8778,7 +8774,7 @@
         <v>-24.1</v>
       </c>
       <c r="O60" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P60" t="e">
         <v>#N/A</v>
@@ -8789,8 +8785,8 @@
       <c r="R60" s="11" t="n">
         <v>25.9</v>
       </c>
-      <c r="S60" t="e">
-        <v>#N/A</v>
+      <c r="S60" t="n">
+        <v>3</v>
       </c>
       <c r="T60" t="e">
         <v>#N/A</v>
@@ -8801,35 +8797,35 @@
       <c r="V60" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="W60" t="e">
-        <v>#N/A</v>
+      <c r="W60" t="n">
+        <v>0.5</v>
       </c>
       <c r="X60" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y60" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z60" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA60" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AB60" t="e">
-        <v>#N/A</v>
+      <c r="Y60" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AA60" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB60" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC60" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD60" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE60" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF60" t="e">
-        <v>#N/A</v>
+      <c r="AD60" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE60" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF60" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG60" t="e">
         <v>#N/A</v>
@@ -8841,17 +8837,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ60" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="61" ht="19" customHeight="1">
       <c r="A61" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B61" t="s">
         <v>271</v>
       </c>
-      <c r="C61" s="34" t="s">
+      <c r="C61" t="s">
         <v>272</v>
       </c>
       <c r="D61" t="s">
@@ -8869,8 +8865,8 @@
       <c r="H61" t="n">
         <v>0.2035</v>
       </c>
-      <c r="I61" t="e">
-        <v>#N/A</v>
+      <c r="I61" t="n">
+        <v>0.004</v>
       </c>
       <c r="J61" t="e">
         <v>#N/A</v>
@@ -8888,7 +8884,7 @@
         <v>-25.2</v>
       </c>
       <c r="O61" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P61" t="e">
         <v>#N/A</v>
@@ -8899,8 +8895,8 @@
       <c r="R61" s="11" t="n">
         <v>25.3</v>
       </c>
-      <c r="S61" t="e">
-        <v>#N/A</v>
+      <c r="S61" t="n">
+        <v>3</v>
       </c>
       <c r="T61" t="e">
         <v>#N/A</v>
@@ -8911,35 +8907,35 @@
       <c r="V61" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="W61" t="e">
-        <v>#N/A</v>
+      <c r="W61" t="n">
+        <v>0.5</v>
       </c>
       <c r="X61" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y61" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z61" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA61" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AB61" t="e">
-        <v>#N/A</v>
+      <c r="Y61" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AA61" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB61" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC61" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD61" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE61" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF61" t="e">
-        <v>#N/A</v>
+      <c r="AD61" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE61" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF61" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG61" t="e">
         <v>#N/A</v>
@@ -8951,17 +8947,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ61" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="62" ht="19" customHeight="1">
       <c r="A62" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B62" t="s">
         <v>271</v>
       </c>
-      <c r="C62" s="34" t="s">
+      <c r="C62" t="s">
         <v>272</v>
       </c>
       <c r="D62" t="s">
@@ -8979,8 +8975,8 @@
       <c r="H62" t="n">
         <v>0.2085</v>
       </c>
-      <c r="I62" t="e">
-        <v>#N/A</v>
+      <c r="I62" t="n">
+        <v>0.004</v>
       </c>
       <c r="J62" t="e">
         <v>#N/A</v>
@@ -8998,7 +8994,7 @@
         <v>-25.8</v>
       </c>
       <c r="O62" t="n">
-        <v>0.8</v>
+        <v>0.565685424949238</v>
       </c>
       <c r="P62" t="e">
         <v>#N/A</v>
@@ -9009,8 +9005,8 @@
       <c r="R62" s="11" t="n">
         <v>26.6</v>
       </c>
-      <c r="S62" t="e">
-        <v>#N/A</v>
+      <c r="S62" t="n">
+        <v>3</v>
       </c>
       <c r="T62" t="e">
         <v>#N/A</v>
@@ -9021,35 +9017,35 @@
       <c r="V62" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="W62" t="e">
-        <v>#N/A</v>
+      <c r="W62" t="n">
+        <v>0.5</v>
       </c>
       <c r="X62" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y62" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z62" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA62" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AB62" t="e">
-        <v>#N/A</v>
+      <c r="Y62" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AA62" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC62" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD62" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE62" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF62" t="e">
-        <v>#N/A</v>
+      <c r="AD62" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE62" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF62" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG62" t="e">
         <v>#N/A</v>
@@ -9061,17 +9057,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ62" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="63" ht="19" customHeight="1">
       <c r="A63" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B63" t="s">
         <v>271</v>
       </c>
-      <c r="C63" s="34" t="s">
+      <c r="C63" t="s">
         <v>272</v>
       </c>
       <c r="D63" t="s">
@@ -9089,8 +9085,8 @@
       <c r="H63" t="n">
         <v>0.2135</v>
       </c>
-      <c r="I63" t="e">
-        <v>#N/A</v>
+      <c r="I63" t="n">
+        <v>0.004</v>
       </c>
       <c r="J63" t="e">
         <v>#N/A</v>
@@ -9108,7 +9104,7 @@
         <v>-25.8</v>
       </c>
       <c r="O63" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P63" t="e">
         <v>#N/A</v>
@@ -9119,8 +9115,8 @@
       <c r="R63" s="11" t="n">
         <v>26.2</v>
       </c>
-      <c r="S63" t="e">
-        <v>#N/A</v>
+      <c r="S63" t="n">
+        <v>3</v>
       </c>
       <c r="T63" t="e">
         <v>#N/A</v>
@@ -9131,35 +9127,35 @@
       <c r="V63" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="W63" t="e">
-        <v>#N/A</v>
+      <c r="W63" t="n">
+        <v>0.5</v>
       </c>
       <c r="X63" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y63" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z63" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA63" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AB63" t="e">
-        <v>#N/A</v>
+      <c r="Y63" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AA63" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC63" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD63" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE63" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF63" t="e">
-        <v>#N/A</v>
+      <c r="AD63" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE63" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF63" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG63" t="e">
         <v>#N/A</v>
@@ -9171,17 +9167,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ63" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="64" ht="19" customHeight="1">
       <c r="A64" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B64" t="s">
         <v>271</v>
       </c>
-      <c r="C64" s="34" t="s">
+      <c r="C64" t="s">
         <v>272</v>
       </c>
       <c r="D64" t="s">
@@ -9199,8 +9195,8 @@
       <c r="H64" t="n">
         <v>0.2196</v>
       </c>
-      <c r="I64" t="e">
-        <v>#N/A</v>
+      <c r="I64" t="n">
+        <v>0.004</v>
       </c>
       <c r="J64" t="e">
         <v>#N/A</v>
@@ -9218,7 +9214,7 @@
         <v>-26.5</v>
       </c>
       <c r="O64" t="n">
-        <v>0.8</v>
+        <v>0.565685424949238</v>
       </c>
       <c r="P64" t="e">
         <v>#N/A</v>
@@ -9229,8 +9225,8 @@
       <c r="R64" s="11" t="n">
         <v>26.6</v>
       </c>
-      <c r="S64" t="e">
-        <v>#N/A</v>
+      <c r="S64" t="n">
+        <v>3</v>
       </c>
       <c r="T64" t="e">
         <v>#N/A</v>
@@ -9241,35 +9237,35 @@
       <c r="V64" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="W64" t="e">
-        <v>#N/A</v>
+      <c r="W64" t="n">
+        <v>0.5</v>
       </c>
       <c r="X64" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y64" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z64" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA64" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AB64" t="e">
-        <v>#N/A</v>
+      <c r="Y64" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AA64" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC64" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD64" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE64" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF64" t="e">
-        <v>#N/A</v>
+      <c r="AD64" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE64" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF64" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG64" t="e">
         <v>#N/A</v>
@@ -9281,17 +9277,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ64" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="65" ht="19" customHeight="1">
       <c r="A65" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B65" t="s">
         <v>271</v>
       </c>
-      <c r="C65" s="34" t="s">
+      <c r="C65" t="s">
         <v>272</v>
       </c>
       <c r="D65" t="s">
@@ -9309,8 +9305,8 @@
       <c r="H65" t="n">
         <v>0.2236</v>
       </c>
-      <c r="I65" t="e">
-        <v>#N/A</v>
+      <c r="I65" t="n">
+        <v>0.004</v>
       </c>
       <c r="J65" t="e">
         <v>#N/A</v>
@@ -9328,7 +9324,7 @@
         <v>-25.8</v>
       </c>
       <c r="O65" t="n">
-        <v>0.8</v>
+        <v>0.565685424949238</v>
       </c>
       <c r="P65" t="e">
         <v>#N/A</v>
@@ -9339,8 +9335,8 @@
       <c r="R65" s="11" t="n">
         <v>26.8</v>
       </c>
-      <c r="S65" t="e">
-        <v>#N/A</v>
+      <c r="S65" t="n">
+        <v>3</v>
       </c>
       <c r="T65" t="e">
         <v>#N/A</v>
@@ -9351,35 +9347,35 @@
       <c r="V65" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="W65" t="e">
-        <v>#N/A</v>
+      <c r="W65" t="n">
+        <v>0.5</v>
       </c>
       <c r="X65" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y65" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z65" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA65" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AB65" t="e">
-        <v>#N/A</v>
+      <c r="Y65" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AA65" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC65" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD65" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE65" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF65" t="e">
-        <v>#N/A</v>
+      <c r="AD65" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE65" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF65" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG65" t="e">
         <v>#N/A</v>
@@ -9391,17 +9387,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ65" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="66" ht="19" customHeight="1">
       <c r="A66" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B66" t="s">
         <v>271</v>
       </c>
-      <c r="C66" s="34" t="s">
+      <c r="C66" t="s">
         <v>272</v>
       </c>
       <c r="D66" t="s">
@@ -9419,8 +9415,8 @@
       <c r="H66" t="n">
         <v>0.2276</v>
       </c>
-      <c r="I66" t="e">
-        <v>#N/A</v>
+      <c r="I66" t="n">
+        <v>0.004</v>
       </c>
       <c r="J66" t="e">
         <v>#N/A</v>
@@ -9438,7 +9434,7 @@
         <v>-25.7</v>
       </c>
       <c r="O66" t="n">
-        <v>0.8</v>
+        <v>0.565685424949238</v>
       </c>
       <c r="P66" t="e">
         <v>#N/A</v>
@@ -9449,8 +9445,8 @@
       <c r="R66" s="11" t="n">
         <v>26.7</v>
       </c>
-      <c r="S66" t="e">
-        <v>#N/A</v>
+      <c r="S66" t="n">
+        <v>3</v>
       </c>
       <c r="T66" t="e">
         <v>#N/A</v>
@@ -9461,35 +9457,35 @@
       <c r="V66" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="W66" t="e">
-        <v>#N/A</v>
+      <c r="W66" t="n">
+        <v>0.5</v>
       </c>
       <c r="X66" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y66" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z66" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA66" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AB66" t="e">
-        <v>#N/A</v>
+      <c r="Y66" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AA66" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC66" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD66" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE66" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF66" t="e">
-        <v>#N/A</v>
+      <c r="AD66" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE66" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF66" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG66" t="e">
         <v>#N/A</v>
@@ -9501,17 +9497,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ66" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="67" ht="19" customHeight="1">
       <c r="A67" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B67" t="s">
         <v>271</v>
       </c>
-      <c r="C67" s="34" t="s">
+      <c r="C67" t="s">
         <v>272</v>
       </c>
       <c r="D67" t="s">
@@ -9529,8 +9525,8 @@
       <c r="H67" t="n">
         <v>0.2313</v>
       </c>
-      <c r="I67" t="e">
-        <v>#N/A</v>
+      <c r="I67" t="n">
+        <v>0.004</v>
       </c>
       <c r="J67" t="e">
         <v>#N/A</v>
@@ -9548,7 +9544,7 @@
         <v>-26.2</v>
       </c>
       <c r="O67" t="n">
-        <v>0.8</v>
+        <v>0.565685424949238</v>
       </c>
       <c r="P67" t="e">
         <v>#N/A</v>
@@ -9559,8 +9555,8 @@
       <c r="R67" s="11" t="n">
         <v>26.2</v>
       </c>
-      <c r="S67" t="e">
-        <v>#N/A</v>
+      <c r="S67" t="n">
+        <v>3</v>
       </c>
       <c r="T67" t="e">
         <v>#N/A</v>
@@ -9571,35 +9567,35 @@
       <c r="V67" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="W67" t="e">
-        <v>#N/A</v>
+      <c r="W67" t="n">
+        <v>0.5</v>
       </c>
       <c r="X67" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y67" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z67" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA67" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AB67" t="e">
-        <v>#N/A</v>
+      <c r="Y67" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AA67" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC67" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD67" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE67" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF67" t="e">
-        <v>#N/A</v>
+      <c r="AD67" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE67" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF67" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG67" t="e">
         <v>#N/A</v>
@@ -9611,17 +9607,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ67" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="68" ht="19" customHeight="1">
       <c r="A68" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B68" t="s">
         <v>271</v>
       </c>
-      <c r="C68" s="34" t="s">
+      <c r="C68" t="s">
         <v>272</v>
       </c>
       <c r="D68" t="s">
@@ -9639,8 +9635,8 @@
       <c r="H68" t="n">
         <v>0.2343</v>
       </c>
-      <c r="I68" t="e">
-        <v>#N/A</v>
+      <c r="I68" t="n">
+        <v>0.004</v>
       </c>
       <c r="J68" t="e">
         <v>#N/A</v>
@@ -9658,7 +9654,7 @@
         <v>-26.5</v>
       </c>
       <c r="O68" t="n">
-        <v>0.8</v>
+        <v>0.565685424949238</v>
       </c>
       <c r="P68" t="e">
         <v>#N/A</v>
@@ -9669,8 +9665,8 @@
       <c r="R68" s="11" t="n">
         <v>26.5</v>
       </c>
-      <c r="S68" t="e">
-        <v>#N/A</v>
+      <c r="S68" t="n">
+        <v>3</v>
       </c>
       <c r="T68" t="e">
         <v>#N/A</v>
@@ -9681,35 +9677,35 @@
       <c r="V68" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="W68" t="e">
-        <v>#N/A</v>
+      <c r="W68" t="n">
+        <v>0.5</v>
       </c>
       <c r="X68" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y68" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z68" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA68" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AB68" t="e">
-        <v>#N/A</v>
+      <c r="Y68" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AA68" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB68" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC68" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD68" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE68" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF68" t="e">
-        <v>#N/A</v>
+      <c r="AD68" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE68" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF68" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG68" t="e">
         <v>#N/A</v>
@@ -9721,17 +9717,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ68" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="69" ht="19" customHeight="1">
       <c r="A69" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B69" t="s">
         <v>271</v>
       </c>
-      <c r="C69" s="34" t="s">
+      <c r="C69" t="s">
         <v>272</v>
       </c>
       <c r="D69" t="s">
@@ -9749,8 +9745,8 @@
       <c r="H69" t="n">
         <v>0.249</v>
       </c>
-      <c r="I69" t="e">
-        <v>#N/A</v>
+      <c r="I69" t="n">
+        <v>0.004</v>
       </c>
       <c r="J69" t="e">
         <v>#N/A</v>
@@ -9768,7 +9764,7 @@
         <v>-25.9</v>
       </c>
       <c r="O69" t="n">
-        <v>0.8</v>
+        <v>0.565685424949238</v>
       </c>
       <c r="P69" t="e">
         <v>#N/A</v>
@@ -9779,8 +9775,8 @@
       <c r="R69" s="11" t="n">
         <v>25.4</v>
       </c>
-      <c r="S69" t="e">
-        <v>#N/A</v>
+      <c r="S69" t="n">
+        <v>3</v>
       </c>
       <c r="T69" t="e">
         <v>#N/A</v>
@@ -9791,35 +9787,35 @@
       <c r="V69" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="W69" t="e">
-        <v>#N/A</v>
+      <c r="W69" t="n">
+        <v>0.5</v>
       </c>
       <c r="X69" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y69" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z69" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA69" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AB69" t="e">
-        <v>#N/A</v>
+      <c r="Y69" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AA69" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC69" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD69" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE69" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF69" t="e">
-        <v>#N/A</v>
+      <c r="AD69" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE69" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF69" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG69" t="e">
         <v>#N/A</v>
@@ -9831,17 +9827,17 @@
         <v>#N/A</v>
       </c>
       <c r="AJ69" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="70" ht="19" customHeight="1">
       <c r="A70" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B70" t="s">
         <v>271</v>
       </c>
-      <c r="C70" s="34" t="s">
+      <c r="C70" t="s">
         <v>272</v>
       </c>
       <c r="D70" t="s">
@@ -9859,8 +9855,8 @@
       <c r="H70" t="n">
         <v>0.2528</v>
       </c>
-      <c r="I70" t="e">
-        <v>#N/A</v>
+      <c r="I70" t="n">
+        <v>0.004</v>
       </c>
       <c r="J70" t="e">
         <v>#N/A</v>
@@ -9878,7 +9874,7 @@
         <v>-24.9</v>
       </c>
       <c r="O70" t="n">
-        <v>0.8</v>
+        <v>0.565685424949238</v>
       </c>
       <c r="P70" t="e">
         <v>#N/A</v>
@@ -9889,8 +9885,8 @@
       <c r="R70" s="11" t="n">
         <v>26.3</v>
       </c>
-      <c r="S70" t="e">
-        <v>#N/A</v>
+      <c r="S70" t="n">
+        <v>3</v>
       </c>
       <c r="T70" t="e">
         <v>#N/A</v>
@@ -9901,35 +9897,35 @@
       <c r="V70" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="W70" t="e">
-        <v>#N/A</v>
+      <c r="W70" t="n">
+        <v>0.5</v>
       </c>
       <c r="X70" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y70" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z70" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA70" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AB70" t="e">
-        <v>#N/A</v>
+      <c r="Y70" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Z70" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AA70" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB70" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC70" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD70" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE70" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF70" t="e">
-        <v>#N/A</v>
+      <c r="AD70" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE70" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF70" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG70" t="e">
         <v>#N/A</v>
@@ -9941,7 +9937,7 @@
         <v>#N/A</v>
       </c>
       <c r="AJ70" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="71" ht="19" customHeight="1">
@@ -10094,74 +10090,6 @@
       <formula>#REF!="no"</formula>
     </cfRule>
   </conditionalFormatting>
-  <hyperlinks>
-    <hyperlink ref="C5" r:id="rId1h"/>
-    <hyperlink ref="C6" r:id="rId2h"/>
-    <hyperlink ref="C7" r:id="rId3h"/>
-    <hyperlink ref="C8" r:id="rId4h"/>
-    <hyperlink ref="C9" r:id="rId5h"/>
-    <hyperlink ref="C10" r:id="rId6h"/>
-    <hyperlink ref="C11" r:id="rId7h"/>
-    <hyperlink ref="C12" r:id="rId8h"/>
-    <hyperlink ref="C13" r:id="rId9h"/>
-    <hyperlink ref="C14" r:id="rId10h"/>
-    <hyperlink ref="C15" r:id="rId11h"/>
-    <hyperlink ref="C16" r:id="rId12h"/>
-    <hyperlink ref="C17" r:id="rId13h"/>
-    <hyperlink ref="C18" r:id="rId14h"/>
-    <hyperlink ref="C19" r:id="rId15h"/>
-    <hyperlink ref="C20" r:id="rId16h"/>
-    <hyperlink ref="C21" r:id="rId17h"/>
-    <hyperlink ref="C22" r:id="rId18h"/>
-    <hyperlink ref="C23" r:id="rId19h"/>
-    <hyperlink ref="C24" r:id="rId20h"/>
-    <hyperlink ref="C25" r:id="rId21h"/>
-    <hyperlink ref="C26" r:id="rId22h"/>
-    <hyperlink ref="C27" r:id="rId23h"/>
-    <hyperlink ref="C28" r:id="rId24h"/>
-    <hyperlink ref="C29" r:id="rId25h"/>
-    <hyperlink ref="C30" r:id="rId26h"/>
-    <hyperlink ref="C31" r:id="rId27h"/>
-    <hyperlink ref="C32" r:id="rId28h"/>
-    <hyperlink ref="C33" r:id="rId29h"/>
-    <hyperlink ref="C34" r:id="rId30h"/>
-    <hyperlink ref="C35" r:id="rId31h"/>
-    <hyperlink ref="C36" r:id="rId32h"/>
-    <hyperlink ref="C37" r:id="rId33h"/>
-    <hyperlink ref="C38" r:id="rId34h"/>
-    <hyperlink ref="C39" r:id="rId35h"/>
-    <hyperlink ref="C40" r:id="rId36h"/>
-    <hyperlink ref="C41" r:id="rId37h"/>
-    <hyperlink ref="C42" r:id="rId38h"/>
-    <hyperlink ref="C43" r:id="rId39h"/>
-    <hyperlink ref="C44" r:id="rId40h"/>
-    <hyperlink ref="C45" r:id="rId41h"/>
-    <hyperlink ref="C46" r:id="rId42h"/>
-    <hyperlink ref="C47" r:id="rId43h"/>
-    <hyperlink ref="C48" r:id="rId44h"/>
-    <hyperlink ref="C49" r:id="rId45h"/>
-    <hyperlink ref="C50" r:id="rId46h"/>
-    <hyperlink ref="C51" r:id="rId47h"/>
-    <hyperlink ref="C52" r:id="rId48h"/>
-    <hyperlink ref="C53" r:id="rId49h"/>
-    <hyperlink ref="C54" r:id="rId50h"/>
-    <hyperlink ref="C55" r:id="rId51h"/>
-    <hyperlink ref="C56" r:id="rId52h"/>
-    <hyperlink ref="C57" r:id="rId53h"/>
-    <hyperlink ref="C58" r:id="rId54h"/>
-    <hyperlink ref="C59" r:id="rId55h"/>
-    <hyperlink ref="C60" r:id="rId56h"/>
-    <hyperlink ref="C61" r:id="rId57h"/>
-    <hyperlink ref="C62" r:id="rId58h"/>
-    <hyperlink ref="C63" r:id="rId59h"/>
-    <hyperlink ref="C64" r:id="rId60h"/>
-    <hyperlink ref="C65" r:id="rId61h"/>
-    <hyperlink ref="C66" r:id="rId62h"/>
-    <hyperlink ref="C67" r:id="rId63h"/>
-    <hyperlink ref="C68" r:id="rId64h"/>
-    <hyperlink ref="C69" r:id="rId65h"/>
-    <hyperlink ref="C70" r:id="rId66h"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <extLst>
